--- a/Backtest/24-12-24/NASDAQstock_24-12-24period252RS90.xlsx
+++ b/Backtest/24-12-24/NASDAQstock_24-12-24period252RS90.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Backtest/24-12-24/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A64C48-2291-6348-98DC-BFF34DB07F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -613,12 +619,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -626,8 +632,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -673,17 +686,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +742,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -755,6 +776,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -789,9 +811,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -964,9 +987,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK75"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
@@ -1086,7 +1109,7 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>92.94330518697225</v>
+        <v>92.943305186972253</v>
       </c>
       <c r="C2">
         <v>2030</v>
@@ -1098,13 +1121,13 @@
         <v>2.06</v>
       </c>
       <c r="F2">
-        <v>-0.460929001771767</v>
+        <v>-0.46092900177176699</v>
       </c>
       <c r="G2">
         <v>1.98</v>
       </c>
       <c r="H2">
-        <v>-0.870991301524132</v>
+        <v>-0.87099130152413196</v>
       </c>
       <c r="I2">
         <v>103.6080001831055</v>
@@ -1113,16 +1136,16 @@
         <v>101.7230003356934</v>
       </c>
       <c r="K2">
-        <v>95.38640014648438</v>
+        <v>95.386400146484377</v>
       </c>
       <c r="L2">
-        <v>72.66739992141724</v>
+        <v>72.667399921417243</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P2">
         <v>2</v>
@@ -1137,7 +1160,7 @@
         <v>5</v>
       </c>
       <c r="T2">
-        <v>27.22222222222222</v>
+        <v>27.222222222222221</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -1188,7 +1211,7 @@
         <v>156</v>
       </c>
       <c r="AK2">
-        <v>82.90285959115336</v>
+        <v>82.902859591153359</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1196,7 +1219,7 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>93.99879372738239</v>
+        <v>93.998793727382392</v>
       </c>
       <c r="C3">
         <v>3357</v>
@@ -1208,31 +1231,31 @@
         <v>2.34</v>
       </c>
       <c r="F3">
-        <v>-0.2407203571623364</v>
+        <v>-0.24072035716233639</v>
       </c>
       <c r="G3">
         <v>2.69</v>
       </c>
       <c r="H3">
-        <v>-0.3746046762710906</v>
+        <v>-0.37460467627109062</v>
       </c>
       <c r="I3">
         <v>28.27000007629395</v>
       </c>
       <c r="J3">
-        <v>28.96499996185303</v>
+        <v>28.964999961853032</v>
       </c>
       <c r="K3">
         <v>25.8353999710083</v>
       </c>
       <c r="L3">
-        <v>19.98129999160767</v>
+        <v>19.981299991607671</v>
       </c>
       <c r="M3">
         <v>0.98</v>
       </c>
       <c r="N3">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1274,7 +1297,7 @@
         <v>6100</v>
       </c>
       <c r="AC3">
-        <v>256.29</v>
+        <v>256.29000000000002</v>
       </c>
       <c r="AD3">
         <v>9.09</v>
@@ -1298,7 +1321,7 @@
         <v>157</v>
       </c>
       <c r="AK3">
-        <v>58.5630637721308</v>
+        <v>58.563063772130803</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1306,7 +1329,7 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>99.65319662243667</v>
+        <v>99.653196622436667</v>
       </c>
       <c r="C4">
         <v>432</v>
@@ -1318,25 +1341,25 @@
         <v>5.5</v>
       </c>
       <c r="F4">
-        <v>2.244491489144097</v>
+        <v>2.2444914891440968</v>
       </c>
       <c r="G4">
         <v>7.26</v>
       </c>
       <c r="H4">
-        <v>2.820447263737922</v>
+        <v>2.8204472637379219</v>
       </c>
       <c r="I4">
-        <v>331.102001953125</v>
+        <v>331.10200195312501</v>
       </c>
       <c r="J4">
-        <v>341.4019989013672</v>
+        <v>341.40199890136722</v>
       </c>
       <c r="K4">
-        <v>265.0276989746094</v>
+        <v>265.02769897460939</v>
       </c>
       <c r="L4">
-        <v>130.881049785614</v>
+        <v>130.88104978561401</v>
       </c>
       <c r="M4">
         <v>0.97</v>
@@ -1357,7 +1380,7 @@
         <v>2</v>
       </c>
       <c r="T4">
-        <v>11.11111111111111</v>
+        <v>11.111111111111111</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -1384,7 +1407,7 @@
         <v>313.01</v>
       </c>
       <c r="AC4">
-        <v>312.71</v>
+        <v>312.70999999999998</v>
       </c>
       <c r="AD4">
         <v>113.12</v>
@@ -1416,7 +1439,7 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>96.44149577804583</v>
+        <v>96.441495778045834</v>
       </c>
       <c r="C5">
         <v>1175</v>
@@ -1434,19 +1457,19 @@
         <v>2.25</v>
       </c>
       <c r="H5">
-        <v>-0.682224556709595</v>
+        <v>-0.68222455670959503</v>
       </c>
       <c r="I5">
         <v>458.8700012207031</v>
       </c>
       <c r="J5">
-        <v>477.5989974975586</v>
+        <v>477.59899749755863</v>
       </c>
       <c r="K5">
-        <v>435.5565997314453</v>
+        <v>435.55659973144532</v>
       </c>
       <c r="L5">
-        <v>345.0091999053955</v>
+        <v>345.00919990539552</v>
       </c>
       <c r="M5">
         <v>0.96</v>
@@ -1467,7 +1490,7 @@
         <v>4</v>
       </c>
       <c r="T5">
-        <v>8.888888888888888</v>
+        <v>8.8888888888888875</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -1485,7 +1508,7 @@
         <v>506.47</v>
       </c>
       <c r="Z5">
-        <v>93.29000000000001</v>
+        <v>93.29</v>
       </c>
       <c r="AA5">
         <v>-41.57</v>
@@ -1518,7 +1541,7 @@
         <v>159</v>
       </c>
       <c r="AK5">
-        <v>50.31071184658921</v>
+        <v>50.310711846589207</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1526,7 +1549,7 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>95.88359469240049</v>
+        <v>95.883594692400493</v>
       </c>
       <c r="C6">
         <v>3023</v>
@@ -1538,25 +1561,25 @@
         <v>2.78</v>
       </c>
       <c r="F6">
-        <v>0.1053217986524834</v>
+        <v>0.10532179865248339</v>
       </c>
       <c r="G6">
         <v>3.62</v>
       </c>
       <c r="H6">
-        <v>0.2755918892012031</v>
+        <v>0.27559188920120309</v>
       </c>
       <c r="I6">
-        <v>25.43400001525879</v>
+        <v>25.434000015258789</v>
       </c>
       <c r="J6">
-        <v>25.68250026702881</v>
+        <v>25.682500267028811</v>
       </c>
       <c r="K6">
-        <v>21.2324001121521</v>
+        <v>21.232400112152099</v>
       </c>
       <c r="L6">
-        <v>17.25495000839233</v>
+        <v>17.254950008392331</v>
       </c>
       <c r="M6">
         <v>0.99</v>
@@ -1577,7 +1600,7 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>17.22222222222222</v>
+        <v>17.222222222222221</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -1607,7 +1630,7 @@
         <v>248.36</v>
       </c>
       <c r="AD6">
-        <v>16.1</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="AE6">
         <v>288.89</v>
@@ -1628,7 +1651,7 @@
         <v>160</v>
       </c>
       <c r="AK6">
-        <v>49.67383195739622</v>
+        <v>49.673831957396217</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1636,7 +1659,7 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>97.79855247285887</v>
+        <v>97.798552472858873</v>
       </c>
       <c r="C7">
         <v>70</v>
@@ -1648,7 +1671,7 @@
         <v>4.58</v>
       </c>
       <c r="F7">
-        <v>1.52094879971311</v>
+        <v>1.5209487997131099</v>
       </c>
       <c r="G7">
         <v>4.88</v>
@@ -1657,13 +1680,13 @@
         <v>1.156503365002375</v>
       </c>
       <c r="I7">
-        <v>38.29600067138672</v>
+        <v>38.296000671386722</v>
       </c>
       <c r="J7">
-        <v>38.76300010681152</v>
+        <v>38.763000106811518</v>
       </c>
       <c r="K7">
-        <v>33.10860008239746</v>
+        <v>33.108600082397459</v>
       </c>
       <c r="L7">
         <v>23.55512498855591</v>
@@ -1672,7 +1695,7 @@
         <v>0.99</v>
       </c>
       <c r="N7">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1723,7 +1746,7 @@
         <v>-19.05</v>
       </c>
       <c r="AF7">
-        <v>16.67</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="AG7">
         <v>800</v>
@@ -1746,7 +1769,7 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>94.78287092882992</v>
+        <v>94.782870928829922</v>
       </c>
       <c r="C8">
         <v>1913</v>
@@ -1758,25 +1781,25 @@
         <v>1.73</v>
       </c>
       <c r="F8">
-        <v>-0.7204606186328819</v>
+        <v>-0.72046061863288191</v>
       </c>
       <c r="G8">
         <v>2.65</v>
       </c>
       <c r="H8">
-        <v>-0.4025701199473183</v>
+        <v>-0.40257011994731828</v>
       </c>
       <c r="I8">
-        <v>53.36800003051758</v>
+        <v>53.368000030517578</v>
       </c>
       <c r="J8">
-        <v>54.53200016021729</v>
+        <v>54.532000160217287</v>
       </c>
       <c r="K8">
-        <v>49.4266000366211</v>
+        <v>49.426600036621103</v>
       </c>
       <c r="L8">
-        <v>38.21719990730286</v>
+        <v>38.217199907302863</v>
       </c>
       <c r="M8">
         <v>0.98</v>
@@ -1836,7 +1859,7 @@
         <v>76.47</v>
       </c>
       <c r="AG8">
-        <v>-83.95999999999999</v>
+        <v>-83.96</v>
       </c>
       <c r="AH8" t="s">
         <v>118</v>
@@ -1848,7 +1871,7 @@
         <v>158</v>
       </c>
       <c r="AK8">
-        <v>48.05193222472008</v>
+        <v>48.051932224720083</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1856,7 +1879,7 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>98.2810615199035</v>
+        <v>98.281061519903503</v>
       </c>
       <c r="C9">
         <v>135</v>
@@ -1868,31 +1891,31 @@
         <v>7.29</v>
       </c>
       <c r="F9">
-        <v>3.652253895754387</v>
+        <v>3.6522538957543871</v>
       </c>
       <c r="G9">
         <v>7.8</v>
       </c>
       <c r="H9">
-        <v>3.197980753366996</v>
+        <v>3.1979807533669962</v>
       </c>
       <c r="I9">
-        <v>27.96600036621094</v>
+        <v>27.966000366210942</v>
       </c>
       <c r="J9">
-        <v>30.61400022506714</v>
+        <v>30.614000225067141</v>
       </c>
       <c r="K9">
-        <v>25.72900009155273</v>
+        <v>25.729000091552731</v>
       </c>
       <c r="L9">
-        <v>19.32280003070831</v>
+        <v>19.322800030708311</v>
       </c>
       <c r="M9">
         <v>0.91</v>
       </c>
       <c r="N9">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1922,7 +1945,7 @@
         <v>8.09</v>
       </c>
       <c r="Y9">
-        <v>35.02</v>
+        <v>35.020000000000003</v>
       </c>
       <c r="Z9">
         <v>6.15</v>
@@ -1958,7 +1981,7 @@
         <v>162</v>
       </c>
       <c r="AK9">
-        <v>47.54283330999027</v>
+        <v>47.542833309990272</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1966,7 +1989,7 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>98.74849215922798</v>
+        <v>98.748492159227979</v>
       </c>
       <c r="C10">
         <v>431</v>
@@ -1978,25 +2001,25 @@
         <v>3.67</v>
       </c>
       <c r="F10">
-        <v>0.80527070473246</v>
+        <v>0.80527070473245999</v>
       </c>
       <c r="G10">
         <v>3.7</v>
       </c>
       <c r="H10">
-        <v>0.3315227765536586</v>
+        <v>0.33152277655365858</v>
       </c>
       <c r="I10">
         <v>138.1199981689453</v>
       </c>
       <c r="J10">
-        <v>149.1665000915527</v>
+        <v>149.16650009155271</v>
       </c>
       <c r="K10">
-        <v>140.577200012207</v>
+        <v>140.57720001220699</v>
       </c>
       <c r="L10">
-        <v>98.97895002365112</v>
+        <v>98.978950023651123</v>
       </c>
       <c r="M10">
         <v>0.93</v>
@@ -2029,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>37.77</v>
+        <v>37.770000000000003</v>
       </c>
       <c r="Y10">
         <v>168.67</v>
@@ -2041,13 +2064,13 @@
         <v>111</v>
       </c>
       <c r="AB10">
-        <v>32.27</v>
+        <v>32.270000000000003</v>
       </c>
       <c r="AC10">
         <v>320.5</v>
       </c>
       <c r="AD10">
-        <v>37.16</v>
+        <v>37.159999999999997</v>
       </c>
       <c r="AE10">
         <v>482.61</v>
@@ -2068,7 +2091,7 @@
         <v>163</v>
       </c>
       <c r="AK10">
-        <v>44.24976819688936</v>
+        <v>44.249768196889363</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2076,7 +2099,7 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>90.44028950542823</v>
+        <v>90.440289505428225</v>
       </c>
       <c r="C11">
         <v>1905</v>
@@ -2088,16 +2111,16 @@
         <v>3.7</v>
       </c>
       <c r="F11">
-        <v>0.8288644880834706</v>
+        <v>0.82886448808347057</v>
       </c>
       <c r="G11">
         <v>2.94</v>
       </c>
       <c r="H11">
-        <v>-0.1998206532946676</v>
+        <v>-0.19982065329466761</v>
       </c>
       <c r="I11">
-        <v>27.78399963378906</v>
+        <v>27.783999633789058</v>
       </c>
       <c r="J11">
         <v>26.8417498588562</v>
@@ -2106,7 +2129,7 @@
         <v>26.64409996032715</v>
       </c>
       <c r="L11">
-        <v>20.88697501659393</v>
+        <v>20.886975016593929</v>
       </c>
       <c r="M11">
         <v>1.04</v>
@@ -2127,7 +2150,7 @@
         <v>5</v>
       </c>
       <c r="T11">
-        <v>8.333333333333332</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="U11" t="b">
         <v>1</v>
@@ -2186,7 +2209,7 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>97.76839565741857</v>
+        <v>97.768395657418566</v>
       </c>
       <c r="C12">
         <v>805</v>
@@ -2198,16 +2221,16 @@
         <v>1.79</v>
       </c>
       <c r="F12">
-        <v>-0.6732730519308611</v>
+        <v>-0.67327305193086107</v>
       </c>
       <c r="G12">
         <v>2.37</v>
       </c>
       <c r="H12">
-        <v>-0.5983282256809119</v>
+        <v>-0.59832822568091193</v>
       </c>
       <c r="I12">
-        <v>111.6899993896484</v>
+        <v>111.68999938964841</v>
       </c>
       <c r="J12">
         <v>114.3325004577637</v>
@@ -2216,7 +2239,7 @@
         <v>106.3346002197266</v>
       </c>
       <c r="L12">
-        <v>79.83840009689331</v>
+        <v>79.838400096893309</v>
       </c>
       <c r="M12">
         <v>0.98</v>
@@ -2270,7 +2293,7 @@
         <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>85.70999999999999</v>
+        <v>85.71</v>
       </c>
       <c r="AF12">
         <v>450</v>
@@ -2288,7 +2311,7 @@
         <v>165</v>
       </c>
       <c r="AK12">
-        <v>43.01447627488545</v>
+        <v>43.014476274885453</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2305,10 +2328,10 @@
         <v>198.75</v>
       </c>
       <c r="E13">
-        <v>2.55</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="F13">
-        <v>-0.07556387370526332</v>
+        <v>-7.5563873705263324E-2</v>
       </c>
       <c r="G13">
         <v>3.41</v>
@@ -2317,16 +2340,16 @@
         <v>0.1287733099010078</v>
       </c>
       <c r="I13">
-        <v>198.6260009765625</v>
+        <v>198.62600097656249</v>
       </c>
       <c r="J13">
-        <v>209.279500579834</v>
+        <v>209.27950057983401</v>
       </c>
       <c r="K13">
-        <v>197.7032000732422</v>
+        <v>197.70320007324219</v>
       </c>
       <c r="L13">
-        <v>141.1291999816895</v>
+        <v>141.12919998168951</v>
       </c>
       <c r="M13">
         <v>0.95</v>
@@ -2371,7 +2394,7 @@
         <v>111</v>
       </c>
       <c r="AB13">
-        <v>607.3</v>
+        <v>607.29999999999995</v>
       </c>
       <c r="AC13">
         <v>342.23</v>
@@ -2398,7 +2421,7 @@
         <v>163</v>
       </c>
       <c r="AK13">
-        <v>42.10574883293292</v>
+        <v>42.105748832932917</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2406,7 +2429,7 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>93.51628468033776</v>
+        <v>93.516284680337762</v>
       </c>
       <c r="C14">
         <v>855</v>
@@ -2418,31 +2441,31 @@
         <v>1.59</v>
       </c>
       <c r="F14">
-        <v>-0.8305649409375973</v>
+        <v>-0.83056494093759725</v>
       </c>
       <c r="G14">
         <v>2</v>
       </c>
       <c r="H14">
-        <v>-0.8570085796860181</v>
+        <v>-0.85700857968601807</v>
       </c>
       <c r="I14">
-        <v>906.243994140625</v>
+        <v>906.24399414062498</v>
       </c>
       <c r="J14">
-        <v>906.3119964599609</v>
+        <v>906.31199645996094</v>
       </c>
       <c r="K14">
-        <v>833.4669958496094</v>
+        <v>833.46699584960936</v>
       </c>
       <c r="L14">
-        <v>694.5256494140625</v>
+        <v>694.52564941406251</v>
       </c>
       <c r="M14">
         <v>1</v>
       </c>
       <c r="N14">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P14">
         <v>10</v>
@@ -2457,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>11.11111111111111</v>
+        <v>11.111111111111111</v>
       </c>
       <c r="U14" t="b">
         <v>0</v>
@@ -2481,7 +2504,7 @@
         <v>35.03</v>
       </c>
       <c r="AB14">
-        <v>64.59999999999999</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="AC14">
         <v>44.8</v>
@@ -2508,7 +2531,7 @@
         <v>166</v>
       </c>
       <c r="AK14">
-        <v>38.674582310922</v>
+        <v>38.674582310921998</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2516,16 +2539,16 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>92.43063932448733</v>
+        <v>92.430639324487331</v>
       </c>
       <c r="C15">
         <v>64</v>
       </c>
       <c r="D15">
-        <v>90.34999999999999</v>
+        <v>90.35</v>
       </c>
       <c r="E15">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F15">
         <v>-1.184471691202754</v>
@@ -2534,19 +2557,19 @@
         <v>1.08</v>
       </c>
       <c r="H15">
-        <v>-1.500213784239255</v>
+        <v>-1.5002137842392551</v>
       </c>
       <c r="I15">
-        <v>92.99199981689453</v>
+        <v>92.991999816894534</v>
       </c>
       <c r="J15">
-        <v>93.41499977111816</v>
+        <v>93.414999771118161</v>
       </c>
       <c r="K15">
-        <v>87.47299972534179</v>
+        <v>87.472999725341793</v>
       </c>
       <c r="L15">
-        <v>73.07739963531495</v>
+        <v>73.077399635314947</v>
       </c>
       <c r="M15">
         <v>1</v>
@@ -2567,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>6.11111111111111</v>
+        <v>6.1111111111111098</v>
       </c>
       <c r="U15" t="b">
         <v>0</v>
@@ -2582,7 +2605,7 @@
         <v>51.72</v>
       </c>
       <c r="Y15">
-        <v>96.18000000000001</v>
+        <v>96.18</v>
       </c>
       <c r="Z15">
         <v>744.53</v>
@@ -2594,7 +2617,7 @@
         <v>11.92</v>
       </c>
       <c r="AC15">
-        <v>913.0599999999999</v>
+        <v>913.06</v>
       </c>
       <c r="AD15">
         <v>23.48</v>
@@ -2618,7 +2641,7 @@
         <v>167</v>
       </c>
       <c r="AK15">
-        <v>37.69222954147668</v>
+        <v>37.692229541476678</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2626,7 +2649,7 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>94.49638118214716</v>
+        <v>94.496381182147161</v>
       </c>
       <c r="C16">
         <v>666</v>
@@ -2638,25 +2661,25 @@
         <v>2.25</v>
       </c>
       <c r="F16">
-        <v>-0.3115017072153676</v>
+        <v>-0.31150170721536757</v>
       </c>
       <c r="G16">
         <v>3.18</v>
       </c>
       <c r="H16">
-        <v>-0.03202799123730132</v>
+        <v>-3.2027991237301323E-2</v>
       </c>
       <c r="I16">
-        <v>10.07600002288818</v>
+        <v>10.076000022888181</v>
       </c>
       <c r="J16">
         <v>10.48399996757507</v>
       </c>
       <c r="K16">
-        <v>9.832800045013428</v>
+        <v>9.8328000450134283</v>
       </c>
       <c r="L16">
-        <v>6.910350000858307</v>
+        <v>6.9103500008583074</v>
       </c>
       <c r="M16">
         <v>0.96</v>
@@ -2728,7 +2751,7 @@
         <v>168</v>
       </c>
       <c r="AK16">
-        <v>37.61993741936924</v>
+        <v>37.619937419369244</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2736,7 +2759,7 @@
         <v>52</v>
       </c>
       <c r="B17">
-        <v>94.63208685162847</v>
+        <v>94.632086851628472</v>
       </c>
       <c r="C17">
         <v>1170</v>
@@ -2748,25 +2771,25 @@
         <v>1.63</v>
       </c>
       <c r="F17">
-        <v>-0.7991065631362502</v>
+        <v>-0.79910656313625017</v>
       </c>
       <c r="G17">
         <v>1.97</v>
       </c>
       <c r="H17">
-        <v>-0.8779826624431888</v>
+        <v>-0.87798266244318879</v>
       </c>
       <c r="I17">
-        <v>76.79200134277343</v>
+        <v>76.792001342773432</v>
       </c>
       <c r="J17">
-        <v>78.62600021362304</v>
+        <v>78.626000213623044</v>
       </c>
       <c r="K17">
-        <v>72.83180015563966</v>
+        <v>72.831800155639655</v>
       </c>
       <c r="L17">
-        <v>56.45270000457764</v>
+        <v>56.452700004577643</v>
       </c>
       <c r="M17">
         <v>0.98</v>
@@ -2799,13 +2822,13 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>38.77</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="Y17">
-        <v>82.04000000000001</v>
+        <v>82.04</v>
       </c>
       <c r="Z17">
-        <v>16.15</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="AA17">
         <v>-1.01</v>
@@ -2826,7 +2849,7 @@
         <v>-2.94</v>
       </c>
       <c r="AG17">
-        <v>134.48</v>
+        <v>134.47999999999999</v>
       </c>
       <c r="AH17" t="s">
         <v>123</v>
@@ -2838,7 +2861,7 @@
         <v>161</v>
       </c>
       <c r="AK17">
-        <v>37.57311111330097</v>
+        <v>37.573111113300968</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2846,7 +2869,7 @@
         <v>53</v>
       </c>
       <c r="B18">
-        <v>90.42521109770809</v>
+        <v>90.425211097708086</v>
       </c>
       <c r="C18">
         <v>29</v>
@@ -2858,7 +2881,7 @@
         <v>3.2</v>
       </c>
       <c r="F18">
-        <v>0.4356347655666299</v>
+        <v>0.43563476556662989</v>
       </c>
       <c r="G18">
         <v>3.52</v>
@@ -2867,7 +2890,7 @@
         <v>0.2056782800106339</v>
       </c>
       <c r="I18">
-        <v>15.58199996948242</v>
+        <v>15.581999969482419</v>
       </c>
       <c r="J18">
         <v>15.86199989318848</v>
@@ -2876,13 +2899,13 @@
         <v>13.54199996948242</v>
       </c>
       <c r="L18">
-        <v>8.815374989509582</v>
+        <v>8.8153749895095821</v>
       </c>
       <c r="M18">
         <v>0.98</v>
       </c>
       <c r="N18">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2897,7 +2920,7 @@
         <v>2</v>
       </c>
       <c r="T18">
-        <v>4.444444444444444</v>
+        <v>4.4444444444444438</v>
       </c>
       <c r="U18" t="b">
         <v>0</v>
@@ -2912,7 +2935,7 @@
         <v>6.01</v>
       </c>
       <c r="Y18">
-        <v>17.19</v>
+        <v>17.190000000000001</v>
       </c>
       <c r="Z18">
         <v>17.38</v>
@@ -2948,7 +2971,7 @@
         <v>169</v>
       </c>
       <c r="AK18">
-        <v>37.20020137090736</v>
+        <v>37.200201370907358</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2956,7 +2979,7 @@
         <v>54</v>
       </c>
       <c r="B19">
-        <v>97.18033775633293</v>
+        <v>97.180337756332932</v>
       </c>
       <c r="C19">
         <v>3577</v>
@@ -2968,25 +2991,25 @@
         <v>2.63</v>
       </c>
       <c r="F19">
-        <v>-0.01264711810256875</v>
+        <v>-1.2647118102568749E-2</v>
       </c>
       <c r="G19">
         <v>3.86</v>
       </c>
       <c r="H19">
-        <v>0.4433845512585691</v>
+        <v>0.44338455125856913</v>
       </c>
       <c r="I19">
-        <v>19.81799964904785</v>
+        <v>19.817999649047849</v>
       </c>
       <c r="J19">
-        <v>19.94049978256226</v>
+        <v>19.940499782562259</v>
       </c>
       <c r="K19">
-        <v>16.05779983520508</v>
+        <v>16.057799835205081</v>
       </c>
       <c r="L19">
-        <v>11.58502495288849</v>
+        <v>11.585024952888491</v>
       </c>
       <c r="M19">
         <v>0.99</v>
@@ -3034,7 +3057,7 @@
         <v>172.46</v>
       </c>
       <c r="AC19">
-        <v>320.47</v>
+        <v>320.47000000000003</v>
       </c>
       <c r="AD19">
         <v>2</v>
@@ -3058,7 +3081,7 @@
         <v>158</v>
       </c>
       <c r="AK19">
-        <v>36.71669181918364</v>
+        <v>36.716691819183637</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -3066,7 +3089,7 @@
         <v>55</v>
       </c>
       <c r="B20">
-        <v>94.04402895054282</v>
+        <v>94.044028950542824</v>
       </c>
       <c r="C20">
         <v>1770</v>
@@ -3078,22 +3101,22 @@
         <v>2.4</v>
       </c>
       <c r="F20">
-        <v>-0.1935327904603155</v>
+        <v>-0.19353279046031549</v>
       </c>
       <c r="G20">
         <v>2.04</v>
       </c>
       <c r="H20">
-        <v>-0.8290431360097903</v>
+        <v>-0.82904313600979029</v>
       </c>
       <c r="I20">
-        <v>134.8200012207031</v>
+        <v>134.82000122070309</v>
       </c>
       <c r="J20">
-        <v>139.2470016479492</v>
+        <v>139.24700164794919</v>
       </c>
       <c r="K20">
-        <v>135.1230001831055</v>
+        <v>135.12300018310549</v>
       </c>
       <c r="L20">
         <v>112.4455500411987</v>
@@ -3141,7 +3164,7 @@
         <v>111</v>
       </c>
       <c r="AB20">
-        <v>86.70999999999999</v>
+        <v>86.71</v>
       </c>
       <c r="AC20">
         <v>562.4</v>
@@ -3168,7 +3191,7 @@
         <v>170</v>
       </c>
       <c r="AK20">
-        <v>36.13678544661703</v>
+        <v>36.136785446617033</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3176,7 +3199,7 @@
         <v>56</v>
       </c>
       <c r="B21">
-        <v>90.93787696019299</v>
+        <v>90.937876960192995</v>
       </c>
       <c r="C21">
         <v>375</v>
@@ -3185,34 +3208,34 @@
         <v>11.19</v>
       </c>
       <c r="E21">
-        <v>4.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F21">
-        <v>1.080531510494248</v>
+        <v>1.0805315104942479</v>
       </c>
       <c r="G21">
         <v>3.63</v>
       </c>
       <c r="H21">
-        <v>0.2825832501202599</v>
+        <v>0.28258325012025992</v>
       </c>
       <c r="I21">
-        <v>11.0519998550415</v>
+        <v>11.051999855041499</v>
       </c>
       <c r="J21">
         <v>10.76300001144409</v>
       </c>
       <c r="K21">
-        <v>9.658999958038329</v>
+        <v>9.6589999580383292</v>
       </c>
       <c r="L21">
-        <v>8.489049971103668</v>
+        <v>8.4890499711036682</v>
       </c>
       <c r="M21">
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -3278,7 +3301,7 @@
         <v>158</v>
       </c>
       <c r="AK21">
-        <v>36.0115096643184</v>
+        <v>36.011509664318403</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -3286,7 +3309,7 @@
         <v>57</v>
       </c>
       <c r="B22">
-        <v>98.43184559710495</v>
+        <v>98.431845597104953</v>
       </c>
       <c r="C22">
         <v>1940</v>
@@ -3295,7 +3318,7 @@
         <v>18.48</v>
       </c>
       <c r="E22">
-        <v>4.73</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="F22">
         <v>1.638917716468163</v>
@@ -3310,13 +3333,13 @@
         <v>18.05799942016602</v>
       </c>
       <c r="J22">
-        <v>17.33849973678589</v>
+        <v>17.338499736785892</v>
       </c>
       <c r="K22">
         <v>15.47439990997314</v>
       </c>
       <c r="L22">
-        <v>11.17394998311996</v>
+        <v>11.173949983119959</v>
       </c>
       <c r="M22">
         <v>1.04</v>
@@ -3358,7 +3381,7 @@
         <v>4.54</v>
       </c>
       <c r="AA22">
-        <v>36.12</v>
+        <v>36.119999999999997</v>
       </c>
       <c r="AB22">
         <v>111.4</v>
@@ -3367,7 +3390,7 @@
         <v>244.88</v>
       </c>
       <c r="AD22">
-        <v>20.06</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="AE22">
         <v>-34.54</v>
@@ -3388,7 +3411,7 @@
         <v>171</v>
       </c>
       <c r="AK22">
-        <v>35.92787266738527</v>
+        <v>35.927872667385273</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3396,7 +3419,7 @@
         <v>58</v>
       </c>
       <c r="B23">
-        <v>90.07840772014475</v>
+        <v>90.078407720144753</v>
       </c>
       <c r="C23">
         <v>2897</v>
@@ -3408,31 +3431,31 @@
         <v>1.44</v>
       </c>
       <c r="F23">
-        <v>-0.9485338576926495</v>
+        <v>-0.94853385769264953</v>
       </c>
       <c r="G23">
         <v>2.72</v>
       </c>
       <c r="H23">
-        <v>-0.3536305935139196</v>
+        <v>-0.35363059351391962</v>
       </c>
       <c r="I23">
-        <v>56.28600006103515</v>
+        <v>56.286000061035153</v>
       </c>
       <c r="J23">
-        <v>57.275</v>
+        <v>57.274999999999999</v>
       </c>
       <c r="K23">
-        <v>51.7292000579834</v>
+        <v>51.729200057983398</v>
       </c>
       <c r="L23">
-        <v>48.13265001296997</v>
+        <v>48.132650012969968</v>
       </c>
       <c r="M23">
         <v>0.98</v>
       </c>
       <c r="N23">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -3468,13 +3491,13 @@
         <v>2.83</v>
       </c>
       <c r="AA23">
-        <v>19.85</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="AB23">
         <v>275.98</v>
       </c>
       <c r="AC23">
-        <v>76.04000000000001</v>
+        <v>76.040000000000006</v>
       </c>
       <c r="AD23">
         <v>1.54</v>
@@ -3498,7 +3521,7 @@
         <v>172</v>
       </c>
       <c r="AK23">
-        <v>35.04760353114085</v>
+        <v>35.047603531140851</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3506,7 +3529,7 @@
         <v>59</v>
       </c>
       <c r="B24">
-        <v>92.61158021712907</v>
+        <v>92.611580217129074</v>
       </c>
       <c r="C24">
         <v>2374</v>
@@ -3518,13 +3541,13 @@
         <v>1.52</v>
       </c>
       <c r="F24">
-        <v>-0.885617102089955</v>
+        <v>-0.88561710208995503</v>
       </c>
       <c r="G24">
         <v>5.47</v>
       </c>
       <c r="H24">
-        <v>1.568993659226733</v>
+        <v>1.5689936592267331</v>
       </c>
       <c r="I24">
         <v>105.7899993896484</v>
@@ -3533,16 +3556,16 @@
         <v>107.4550006866455</v>
       </c>
       <c r="K24">
-        <v>97.14940048217774</v>
+        <v>97.149400482177739</v>
       </c>
       <c r="L24">
-        <v>77.93274980545044</v>
+        <v>77.932749805450442</v>
       </c>
       <c r="M24">
         <v>0.98</v>
       </c>
       <c r="N24">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -3575,7 +3598,7 @@
         <v>112.8</v>
       </c>
       <c r="Z24">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AA24">
         <v>38.85</v>
@@ -3593,7 +3616,7 @@
         <v>-35.81</v>
       </c>
       <c r="AF24">
-        <v>-9.199999999999999</v>
+        <v>-9.1999999999999993</v>
       </c>
       <c r="AG24">
         <v>3.82</v>
@@ -3608,7 +3631,7 @@
         <v>160</v>
       </c>
       <c r="AK24">
-        <v>33.91786088965283</v>
+        <v>33.917860889652829</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -3616,7 +3639,7 @@
         <v>60</v>
       </c>
       <c r="B25">
-        <v>99.77382388419784</v>
+        <v>99.773823884197839</v>
       </c>
       <c r="C25">
         <v>2790</v>
@@ -3631,22 +3654,22 @@
         <v>2.511887700455548</v>
       </c>
       <c r="G25">
-        <v>8.289999999999999</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="H25">
-        <v>3.540557438400784</v>
+        <v>3.5405574384007839</v>
       </c>
       <c r="I25">
-        <v>91.37599945068359</v>
+        <v>91.375999450683594</v>
       </c>
       <c r="J25">
-        <v>90.36049995422363</v>
+        <v>90.360499954223627</v>
       </c>
       <c r="K25">
-        <v>68.65619995117187</v>
+        <v>68.656199951171871</v>
       </c>
       <c r="L25">
-        <v>45.96730003356934</v>
+        <v>45.967300033569337</v>
       </c>
       <c r="M25">
         <v>1.01</v>
@@ -3697,13 +3720,13 @@
         <v>103.31</v>
       </c>
       <c r="AD25">
-        <v>35.12</v>
+        <v>35.119999999999997</v>
       </c>
       <c r="AE25">
         <v>-92.16</v>
       </c>
       <c r="AF25">
-        <v>-81.79000000000001</v>
+        <v>-81.790000000000006</v>
       </c>
       <c r="AG25">
         <v>9233.33</v>
@@ -3718,7 +3741,7 @@
         <v>158</v>
       </c>
       <c r="AK25">
-        <v>33.37549548511249</v>
+        <v>33.375495485112488</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -3726,7 +3749,7 @@
         <v>61</v>
       </c>
       <c r="B26">
-        <v>93.54644149577804</v>
+        <v>93.546441495778041</v>
       </c>
       <c r="C26">
         <v>1961</v>
@@ -3738,22 +3761,22 @@
         <v>3.73</v>
       </c>
       <c r="F26">
-        <v>0.8524582714344808</v>
+        <v>0.85245827143448083</v>
       </c>
       <c r="G26">
         <v>4.59</v>
       </c>
       <c r="H26">
-        <v>0.9537538983497242</v>
+        <v>0.95375389834972424</v>
       </c>
       <c r="I26">
-        <v>34.34199905395508</v>
+        <v>34.341999053955078</v>
       </c>
       <c r="J26">
-        <v>36.27449951171875</v>
+        <v>36.274499511718751</v>
       </c>
       <c r="K26">
-        <v>31.89859966278076</v>
+        <v>31.898599662780761</v>
       </c>
       <c r="L26">
         <v>23.26644989490509</v>
@@ -3807,7 +3830,7 @@
         <v>255.92</v>
       </c>
       <c r="AD26">
-        <v>9.970000000000001</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="AE26">
         <v>-27.27</v>
@@ -3828,7 +3851,7 @@
         <v>165</v>
       </c>
       <c r="AK26">
-        <v>31.90120071852455</v>
+        <v>31.901200718524549</v>
       </c>
     </row>
     <row r="27" spans="1:37">
@@ -3848,25 +3871,25 @@
         <v>3.58</v>
       </c>
       <c r="F27">
-        <v>0.7344893546794288</v>
+        <v>0.73448935467942877</v>
       </c>
       <c r="G27">
         <v>3.77</v>
       </c>
       <c r="H27">
-        <v>0.3804623029870569</v>
+        <v>0.38046230298705691</v>
       </c>
       <c r="I27">
-        <v>95.18799896240235</v>
+        <v>95.187998962402347</v>
       </c>
       <c r="J27">
-        <v>91.25349960327148</v>
+        <v>91.253499603271479</v>
       </c>
       <c r="K27">
-        <v>80.63580009460449</v>
+        <v>80.635800094604491</v>
       </c>
       <c r="L27">
-        <v>58.23085000991821</v>
+        <v>58.230850009918207</v>
       </c>
       <c r="M27">
         <v>1.04</v>
@@ -3887,7 +3910,7 @@
         <v>4</v>
       </c>
       <c r="T27">
-        <v>8.888888888888888</v>
+        <v>8.8888888888888875</v>
       </c>
       <c r="U27" t="b">
         <v>0</v>
@@ -3938,7 +3961,7 @@
         <v>173</v>
       </c>
       <c r="AK27">
-        <v>31.4224553158678</v>
+        <v>31.422455315867801</v>
       </c>
     </row>
     <row r="28" spans="1:37">
@@ -3946,7 +3969,7 @@
         <v>63</v>
       </c>
       <c r="B28">
-        <v>94.61700844390832</v>
+        <v>94.617008443908318</v>
       </c>
       <c r="C28">
         <v>1910</v>
@@ -3958,25 +3981,25 @@
         <v>1.95</v>
       </c>
       <c r="F28">
-        <v>-0.5474395407254721</v>
+        <v>-0.54743954072547207</v>
       </c>
       <c r="G28">
-        <v>4.65</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="H28">
-        <v>0.9957020638640661</v>
+        <v>0.99570206386406612</v>
       </c>
       <c r="I28">
         <v>24.82600021362305</v>
       </c>
       <c r="J28">
-        <v>25.97100009918213</v>
+        <v>25.971000099182131</v>
       </c>
       <c r="K28">
-        <v>23.60879993438721</v>
+        <v>23.608799934387211</v>
       </c>
       <c r="L28">
-        <v>18.28619995594025</v>
+        <v>18.286199955940251</v>
       </c>
       <c r="M28">
         <v>0.96</v>
@@ -4018,7 +4041,7 @@
         <v>1.47</v>
       </c>
       <c r="AA28">
-        <v>-2.24</v>
+        <v>-2.2400000000000002</v>
       </c>
       <c r="AB28">
         <v>40.33</v>
@@ -4056,7 +4079,7 @@
         <v>64</v>
       </c>
       <c r="B29">
-        <v>96.78829915560917</v>
+        <v>96.788299155609167</v>
       </c>
       <c r="C29">
         <v>4756</v>
@@ -4068,7 +4091,7 @@
         <v>2.4</v>
       </c>
       <c r="F29">
-        <v>-0.1935327904603155</v>
+        <v>-0.19353279046031549</v>
       </c>
       <c r="G29">
         <v>3.41</v>
@@ -4077,22 +4100,22 @@
         <v>0.1287733099010078</v>
       </c>
       <c r="I29">
-        <v>338.0719970703125</v>
+        <v>338.07199707031248</v>
       </c>
       <c r="J29">
-        <v>344.3630035400391</v>
+        <v>344.36300354003907</v>
       </c>
       <c r="K29">
-        <v>309.7922021484375</v>
+        <v>309.79220214843753</v>
       </c>
       <c r="L29">
-        <v>194.5270509719849</v>
+        <v>194.52705097198489</v>
       </c>
       <c r="M29">
         <v>0.98</v>
       </c>
       <c r="N29">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P29">
         <v>4</v>
@@ -4137,7 +4160,7 @@
         <v>45.75</v>
       </c>
       <c r="AD29">
-        <v>623.9400000000001</v>
+        <v>623.94000000000005</v>
       </c>
       <c r="AE29">
         <v>23.26</v>
@@ -4158,7 +4181,7 @@
         <v>175</v>
       </c>
       <c r="AK29">
-        <v>28.26333535644232</v>
+        <v>28.263335356442319</v>
       </c>
     </row>
     <row r="30" spans="1:37">
@@ -4166,7 +4189,7 @@
         <v>65</v>
       </c>
       <c r="B30">
-        <v>93.4258142340169</v>
+        <v>93.425814234016897</v>
       </c>
       <c r="C30">
         <v>2685</v>
@@ -4178,31 +4201,31 @@
         <v>3.3</v>
       </c>
       <c r="F30">
-        <v>0.5142807100699978</v>
+        <v>0.51428071006999776</v>
       </c>
       <c r="G30">
         <v>4.76</v>
       </c>
       <c r="H30">
-        <v>1.072607033973692</v>
+        <v>1.0726070339736919</v>
       </c>
       <c r="I30">
-        <v>33.98600006103516</v>
+        <v>33.986000061035163</v>
       </c>
       <c r="J30">
-        <v>35.57100009918213</v>
+        <v>35.571000099182129</v>
       </c>
       <c r="K30">
-        <v>30.94400009155273</v>
+        <v>30.944000091552731</v>
       </c>
       <c r="L30">
-        <v>23.17635000228882</v>
+        <v>23.176350002288821</v>
       </c>
       <c r="M30">
         <v>0.96</v>
       </c>
       <c r="N30">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -4247,7 +4270,7 @@
         <v>122.64</v>
       </c>
       <c r="AD30">
-        <v>9.119999999999999</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="AE30">
         <v>50</v>
@@ -4268,7 +4291,7 @@
         <v>168</v>
       </c>
       <c r="AK30">
-        <v>28.16913146126526</v>
+        <v>28.169131461265259</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -4282,31 +4305,31 @@
         <v>1344</v>
       </c>
       <c r="D31">
-        <v>16.17</v>
+        <v>16.170000000000002</v>
       </c>
       <c r="E31">
         <v>2.59</v>
       </c>
       <c r="F31">
-        <v>-0.04410549590391603</v>
+        <v>-4.4105495903916027E-2</v>
       </c>
       <c r="G31">
         <v>3.49</v>
       </c>
       <c r="H31">
-        <v>0.1847041972534633</v>
+        <v>0.18470419725346329</v>
       </c>
       <c r="I31">
-        <v>16.12800006866455</v>
+        <v>16.128000068664551</v>
       </c>
       <c r="J31">
-        <v>16.71450009346008</v>
+        <v>16.714500093460082</v>
       </c>
       <c r="K31">
-        <v>14.95659997940063</v>
+        <v>14.956599979400631</v>
       </c>
       <c r="L31">
-        <v>12.85559998989105</v>
+        <v>12.855599989891051</v>
       </c>
       <c r="M31">
         <v>0.96</v>
@@ -4339,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="X31">
-        <v>8.380000000000001</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="Y31">
         <v>18.38</v>
@@ -4351,13 +4374,13 @@
         <v>1.08</v>
       </c>
       <c r="AB31">
-        <v>40.87</v>
+        <v>40.869999999999997</v>
       </c>
       <c r="AC31">
         <v>127.59</v>
       </c>
       <c r="AD31">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="AE31">
         <v>500</v>
@@ -4366,7 +4389,7 @@
         <v>92.31</v>
       </c>
       <c r="AG31">
-        <v>-156.52</v>
+        <v>-156.52000000000001</v>
       </c>
       <c r="AH31" t="s">
         <v>125</v>
@@ -4378,7 +4401,7 @@
         <v>176</v>
       </c>
       <c r="AK31">
-        <v>27.29688257866937</v>
+        <v>27.296882578669369</v>
       </c>
     </row>
     <row r="32" spans="1:37">
@@ -4386,7 +4409,7 @@
         <v>67</v>
       </c>
       <c r="B32">
-        <v>95.64234016887816</v>
+        <v>95.642340168878164</v>
       </c>
       <c r="C32">
         <v>1653</v>
@@ -4398,25 +4421,25 @@
         <v>1.55</v>
       </c>
       <c r="F32">
-        <v>-0.8620233187389446</v>
+        <v>-0.86202331873894456</v>
       </c>
       <c r="G32">
         <v>2.14</v>
       </c>
       <c r="H32">
-        <v>-0.7591295268192211</v>
+        <v>-0.75912952681922108</v>
       </c>
       <c r="I32">
         <v>175.9999969482422</v>
       </c>
       <c r="J32">
-        <v>182.7839981079102</v>
+        <v>182.78399810791021</v>
       </c>
       <c r="K32">
-        <v>171.251399230957</v>
+        <v>171.25139923095699</v>
       </c>
       <c r="L32">
-        <v>134.2631000518799</v>
+        <v>134.26310005187989</v>
       </c>
       <c r="M32">
         <v>0.96</v>
@@ -4437,7 +4460,7 @@
         <v>1</v>
       </c>
       <c r="T32">
-        <v>11.11111111111111</v>
+        <v>11.111111111111111</v>
       </c>
       <c r="U32" t="b">
         <v>1</v>
@@ -4473,7 +4496,7 @@
         <v>0.6</v>
       </c>
       <c r="AF32">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="AG32">
         <v>8.67</v>
@@ -4508,31 +4531,31 @@
         <v>3.16</v>
       </c>
       <c r="F33">
-        <v>0.4041763877652826</v>
+        <v>0.40417638776528259</v>
       </c>
       <c r="G33">
         <v>3.35</v>
       </c>
       <c r="H33">
-        <v>0.08682514438666628</v>
+        <v>8.6825144386666275E-2</v>
       </c>
       <c r="I33">
         <v>16.68999977111816</v>
       </c>
       <c r="J33">
-        <v>16.32949986457825</v>
+        <v>16.329499864578249</v>
       </c>
       <c r="K33">
         <v>15.10239992141724</v>
       </c>
       <c r="L33">
-        <v>10.98129999399185</v>
+        <v>10.981299993991851</v>
       </c>
       <c r="M33">
         <v>1.02</v>
       </c>
       <c r="N33">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -4577,7 +4600,7 @@
         <v>176.47</v>
       </c>
       <c r="AD33">
-        <v>4.06</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="AE33">
         <v>0</v>
@@ -4598,7 +4621,7 @@
         <v>171</v>
       </c>
       <c r="AK33">
-        <v>27.06740974429607</v>
+        <v>27.067409744296071</v>
       </c>
     </row>
     <row r="34" spans="1:37">
@@ -4606,7 +4629,7 @@
         <v>69</v>
       </c>
       <c r="B34">
-        <v>92.74728588661037</v>
+        <v>92.747285886610371</v>
       </c>
       <c r="C34">
         <v>1102</v>
@@ -4618,31 +4641,31 @@
         <v>2.08</v>
       </c>
       <c r="F34">
-        <v>-0.4451998128710934</v>
+        <v>-0.44519981287109339</v>
       </c>
       <c r="G34">
         <v>4.3</v>
       </c>
       <c r="H34">
-        <v>0.7510044316970735</v>
+        <v>0.75100443169707354</v>
       </c>
       <c r="I34">
-        <v>52.71399993896485</v>
+        <v>52.713999938964847</v>
       </c>
       <c r="J34">
-        <v>53.21250019073486</v>
+        <v>53.212500190734858</v>
       </c>
       <c r="K34">
-        <v>45.37100021362305</v>
+        <v>45.371000213623049</v>
       </c>
       <c r="L34">
-        <v>37.23394999504089</v>
+        <v>37.233949995040888</v>
       </c>
       <c r="M34">
         <v>0.99</v>
       </c>
       <c r="N34">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -4675,7 +4698,7 @@
         <v>56.1</v>
       </c>
       <c r="Z34">
-        <v>8.449999999999999</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="AA34">
         <v>-53.03</v>
@@ -4716,7 +4739,7 @@
         <v>70</v>
       </c>
       <c r="B35">
-        <v>99.1254523522316</v>
+        <v>99.125452352231605</v>
       </c>
       <c r="C35">
         <v>9</v>
@@ -4728,22 +4751,22 @@
         <v>3.5</v>
       </c>
       <c r="F35">
-        <v>0.6715725990767342</v>
+        <v>0.67157259907673417</v>
       </c>
       <c r="G35">
         <v>4.47</v>
       </c>
       <c r="H35">
-        <v>0.8698575673210411</v>
+        <v>0.86985756732104114</v>
       </c>
       <c r="I35">
-        <v>76.27000122070312</v>
+        <v>76.270001220703122</v>
       </c>
       <c r="J35">
-        <v>72.05800018310546</v>
+        <v>72.058000183105463</v>
       </c>
       <c r="K35">
-        <v>59.35520004272461</v>
+        <v>59.355200042724611</v>
       </c>
       <c r="L35">
         <v>35.27569996833801</v>
@@ -4818,7 +4841,7 @@
         <v>168</v>
       </c>
       <c r="AK35">
-        <v>26.88742683098394</v>
+        <v>26.887426830983941</v>
       </c>
     </row>
     <row r="36" spans="1:37">
@@ -4832,28 +4855,28 @@
         <v>1528.5</v>
       </c>
       <c r="D36">
-        <v>38.2</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="E36">
         <v>3.22</v>
       </c>
       <c r="F36">
-        <v>0.4513639544673035</v>
+        <v>0.45136395446730349</v>
       </c>
       <c r="G36">
         <v>3.39</v>
       </c>
       <c r="H36">
-        <v>0.114790588062894</v>
+        <v>0.11479058806289399</v>
       </c>
       <c r="I36">
         <v>38.3620002746582</v>
       </c>
       <c r="J36">
-        <v>37.43600006103516</v>
+        <v>37.436000061035159</v>
       </c>
       <c r="K36">
-        <v>34.70689998626709</v>
+        <v>34.706899986267089</v>
       </c>
       <c r="L36">
         <v>24.87122502803803</v>
@@ -4862,7 +4885,7 @@
         <v>1.02</v>
       </c>
       <c r="N36">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -4928,7 +4951,7 @@
         <v>169</v>
       </c>
       <c r="AK36">
-        <v>26.72536323889098</v>
+        <v>26.725363238890981</v>
       </c>
     </row>
     <row r="37" spans="1:37">
@@ -4936,7 +4959,7 @@
         <v>72</v>
       </c>
       <c r="B37">
-        <v>94.30036188178529</v>
+        <v>94.300361881785292</v>
       </c>
       <c r="C37">
         <v>3643</v>
@@ -4945,16 +4968,16 @@
         <v>30.05</v>
       </c>
       <c r="E37">
-        <v>2.55</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="F37">
-        <v>-0.07556387370526332</v>
+        <v>-7.5563873705263324E-2</v>
       </c>
       <c r="G37">
         <v>2.91</v>
       </c>
       <c r="H37">
-        <v>-0.2207947360518382</v>
+        <v>-0.22079473605183819</v>
       </c>
       <c r="I37">
         <v>29.71800003051758</v>
@@ -5017,7 +5040,7 @@
         <v>174.05</v>
       </c>
       <c r="AD37">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AE37">
         <v>33.33</v>
@@ -5026,7 +5049,7 @@
         <v>12.5</v>
       </c>
       <c r="AG37">
-        <v>71.43000000000001</v>
+        <v>71.430000000000007</v>
       </c>
       <c r="AH37" t="s">
         <v>111</v>
@@ -5038,7 +5061,7 @@
         <v>178</v>
       </c>
       <c r="AK37">
-        <v>26.62886234698586</v>
+        <v>26.628862346985859</v>
       </c>
     </row>
     <row r="38" spans="1:37">
@@ -5046,7 +5069,7 @@
         <v>73</v>
       </c>
       <c r="B38">
-        <v>90.50060313630881</v>
+        <v>90.500603136308811</v>
       </c>
       <c r="C38">
         <v>1126</v>
@@ -5055,7 +5078,7 @@
         <v>72.78</v>
       </c>
       <c r="E38">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F38">
         <v>-1.184471691202754</v>
@@ -5064,19 +5087,19 @@
         <v>1.7</v>
       </c>
       <c r="H38">
-        <v>-1.066749407257726</v>
+        <v>-1.0667494072577259</v>
       </c>
       <c r="I38">
-        <v>71.82400054931641</v>
+        <v>71.824000549316409</v>
       </c>
       <c r="J38">
-        <v>74.27249984741211</v>
+        <v>74.272499847412107</v>
       </c>
       <c r="K38">
-        <v>69.97980010986328</v>
+        <v>69.979800109863277</v>
       </c>
       <c r="L38">
-        <v>57.56410018920899</v>
+        <v>57.564100189208993</v>
       </c>
       <c r="M38">
         <v>0.97</v>
@@ -5097,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="T38">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="U38" t="b">
         <v>1</v>
@@ -5156,7 +5179,7 @@
         <v>74</v>
       </c>
       <c r="B39">
-        <v>94.17973462002412</v>
+        <v>94.179734620024121</v>
       </c>
       <c r="C39">
         <v>4544</v>
@@ -5168,25 +5191,25 @@
         <v>1.77</v>
       </c>
       <c r="F39">
-        <v>-0.6890022408315346</v>
+        <v>-0.68900224083153461</v>
       </c>
       <c r="G39">
         <v>2.5</v>
       </c>
       <c r="H39">
-        <v>-0.507440533733172</v>
+        <v>-0.50744053373317199</v>
       </c>
       <c r="I39">
         <v>23.78199996948242</v>
       </c>
       <c r="J39">
-        <v>24.94774971008301</v>
+        <v>24.947749710083009</v>
       </c>
       <c r="K39">
         <v>23.38309986114502</v>
       </c>
       <c r="L39">
-        <v>17.41419996261597</v>
+        <v>17.414199962615971</v>
       </c>
       <c r="M39">
         <v>0.95</v>
@@ -5225,7 +5248,7 @@
         <v>27</v>
       </c>
       <c r="Z39">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="AA39" t="s">
         <v>111</v>
@@ -5266,7 +5289,7 @@
         <v>75</v>
       </c>
       <c r="B40">
-        <v>92.85283474065139</v>
+        <v>92.852834740651389</v>
       </c>
       <c r="C40">
         <v>2279</v>
@@ -5278,22 +5301,22 @@
         <v>2.52</v>
       </c>
       <c r="F40">
-        <v>-0.09915765705627361</v>
+        <v>-9.9157657056273607E-2</v>
       </c>
       <c r="G40">
         <v>2.84</v>
       </c>
       <c r="H40">
-        <v>-0.2697342624852369</v>
+        <v>-0.26973426248523691</v>
       </c>
       <c r="I40">
         <v>54.83999938964844</v>
       </c>
       <c r="J40">
-        <v>55.58949966430664</v>
+        <v>55.589499664306643</v>
       </c>
       <c r="K40">
-        <v>51.92600006103515</v>
+        <v>51.926000061035147</v>
       </c>
       <c r="L40">
         <v>46.98910011291504</v>
@@ -5347,10 +5370,10 @@
         <v>102.35</v>
       </c>
       <c r="AD40">
-        <v>39.34</v>
+        <v>39.340000000000003</v>
       </c>
       <c r="AE40">
-        <v>19.67</v>
+        <v>19.670000000000002</v>
       </c>
       <c r="AF40">
         <v>76.31</v>
@@ -5368,7 +5391,7 @@
         <v>181</v>
       </c>
       <c r="AK40">
-        <v>24.92059341047417</v>
+        <v>24.920593410474169</v>
       </c>
     </row>
     <row r="41" spans="1:37">
@@ -5376,7 +5399,7 @@
         <v>76</v>
       </c>
       <c r="B41">
-        <v>90.92279855247286</v>
+        <v>90.922798552472855</v>
       </c>
       <c r="C41">
         <v>424</v>
@@ -5388,7 +5411,7 @@
         <v>1.84</v>
       </c>
       <c r="F41">
-        <v>-0.6339500796791769</v>
+        <v>-0.63395007967917694</v>
       </c>
       <c r="G41">
         <v>2.21</v>
@@ -5400,13 +5423,13 @@
         <v>95.88800048828125</v>
       </c>
       <c r="J41">
-        <v>96.57500038146972</v>
+        <v>96.575000381469721</v>
       </c>
       <c r="K41">
         <v>90.02600021362305</v>
       </c>
       <c r="L41">
-        <v>72.29825019836426</v>
+        <v>72.298250198364258</v>
       </c>
       <c r="M41">
         <v>0.99</v>
@@ -5457,7 +5480,7 @@
         <v>71.38</v>
       </c>
       <c r="AD41">
-        <v>311.53</v>
+        <v>311.52999999999997</v>
       </c>
       <c r="AE41">
         <v>42</v>
@@ -5498,7 +5521,7 @@
         <v>2.9</v>
       </c>
       <c r="F42">
-        <v>0.1996969320565253</v>
+        <v>0.19969693205652531</v>
       </c>
       <c r="G42">
         <v>3.4</v>
@@ -5507,22 +5530,22 @@
         <v>0.1217819489819508</v>
       </c>
       <c r="I42">
-        <v>72.83000030517579</v>
+        <v>72.830000305175787</v>
       </c>
       <c r="J42">
         <v>69.77649974822998</v>
       </c>
       <c r="K42">
-        <v>65.86739982604981</v>
+        <v>65.867399826049805</v>
       </c>
       <c r="L42">
-        <v>53.32289989471435</v>
+        <v>53.322899894714347</v>
       </c>
       <c r="M42">
         <v>1.04</v>
       </c>
       <c r="N42">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -5552,7 +5575,7 @@
         <v>33.67</v>
       </c>
       <c r="Y42">
-        <v>77.18000000000001</v>
+        <v>77.180000000000007</v>
       </c>
       <c r="Z42">
         <v>47.08</v>
@@ -5596,7 +5619,7 @@
         <v>78</v>
       </c>
       <c r="B43">
-        <v>91.57117008443907</v>
+        <v>91.571170084439075</v>
       </c>
       <c r="C43">
         <v>2352</v>
@@ -5608,25 +5631,25 @@
         <v>4.07</v>
       </c>
       <c r="F43">
-        <v>1.119854482745933</v>
+        <v>1.1198544827459329</v>
       </c>
       <c r="G43">
         <v>3.17</v>
       </c>
       <c r="H43">
-        <v>-0.03901935215635841</v>
+        <v>-3.9019352156358413E-2</v>
       </c>
       <c r="I43">
-        <v>31.92600021362305</v>
+        <v>31.926000213623048</v>
       </c>
       <c r="J43">
-        <v>31.87450008392334</v>
+        <v>31.874500083923341</v>
       </c>
       <c r="K43">
-        <v>29.96259994506836</v>
+        <v>29.962599945068359</v>
       </c>
       <c r="L43">
-        <v>26.57799998283386</v>
+        <v>26.577999982833859</v>
       </c>
       <c r="M43">
         <v>1</v>
@@ -5706,7 +5729,7 @@
         <v>79</v>
       </c>
       <c r="B44">
-        <v>90.78709288299156</v>
+        <v>90.787092882991558</v>
       </c>
       <c r="C44">
         <v>1134</v>
@@ -5718,13 +5741,13 @@
         <v>3.89</v>
       </c>
       <c r="F44">
-        <v>0.97829178263987</v>
+        <v>0.97829178263987004</v>
       </c>
       <c r="G44">
         <v>3.44</v>
       </c>
       <c r="H44">
-        <v>0.1497473926581785</v>
+        <v>0.14974739265817849</v>
       </c>
       <c r="I44">
         <v>151.6820007324219</v>
@@ -5733,10 +5756,10 @@
         <v>148.7695007324219</v>
       </c>
       <c r="K44">
-        <v>146.3702005004883</v>
+        <v>146.37020050048829</v>
       </c>
       <c r="L44">
-        <v>146.1381499862671</v>
+        <v>146.13814998626711</v>
       </c>
       <c r="M44">
         <v>1.02</v>
@@ -5781,7 +5804,7 @@
         <v>41.99</v>
       </c>
       <c r="AB44">
-        <v>69.09999999999999</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="AC44">
         <v>36.54</v>
@@ -5808,7 +5831,7 @@
         <v>184</v>
       </c>
       <c r="AK44">
-        <v>24.55756195080023</v>
+        <v>24.557561950800231</v>
       </c>
     </row>
     <row r="45" spans="1:37">
@@ -5816,7 +5839,7 @@
         <v>80</v>
       </c>
       <c r="B45">
-        <v>91.37515078407719</v>
+        <v>91.375150784077192</v>
       </c>
       <c r="C45">
         <v>1543</v>
@@ -5828,31 +5851,31 @@
         <v>1.41</v>
       </c>
       <c r="F45">
-        <v>-0.97212764104366</v>
+        <v>-0.97212764104366001</v>
       </c>
       <c r="G45">
         <v>1.32</v>
       </c>
       <c r="H45">
-        <v>-1.332421122181889</v>
+        <v>-1.3324211221818889</v>
       </c>
       <c r="I45">
         <v>46.44600067138672</v>
       </c>
       <c r="J45">
-        <v>44.79900016784668</v>
+        <v>44.799000167846678</v>
       </c>
       <c r="K45">
-        <v>42.33310005187988</v>
+        <v>42.333100051879882</v>
       </c>
       <c r="L45">
-        <v>35.28732491493225</v>
+        <v>35.287324914932249</v>
       </c>
       <c r="M45">
         <v>1.04</v>
       </c>
       <c r="N45">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P45">
         <v>0</v>
@@ -5897,7 +5920,7 @@
         <v>116.32</v>
       </c>
       <c r="AD45">
-        <v>17.74</v>
+        <v>17.739999999999998</v>
       </c>
       <c r="AE45">
         <v>167.16</v>
@@ -5926,7 +5949,7 @@
         <v>81</v>
       </c>
       <c r="B46">
-        <v>90.98311218335344</v>
+        <v>90.983112183353441</v>
       </c>
       <c r="C46">
         <v>388</v>
@@ -5938,31 +5961,31 @@
         <v>1.43</v>
       </c>
       <c r="F46">
-        <v>-0.9563984521429864</v>
+        <v>-0.95639845214298636</v>
       </c>
       <c r="G46">
         <v>1.37</v>
       </c>
       <c r="H46">
-        <v>-1.297464317586604</v>
+        <v>-1.2974643175866041</v>
       </c>
       <c r="I46">
-        <v>49.26399993896484</v>
+        <v>49.263999938964837</v>
       </c>
       <c r="J46">
-        <v>47.28300018310547</v>
+        <v>47.283000183105472</v>
       </c>
       <c r="K46">
-        <v>45.19719993591308</v>
+        <v>45.197199935913083</v>
       </c>
       <c r="L46">
-        <v>37.99459998130799</v>
+        <v>37.994599981307992</v>
       </c>
       <c r="M46">
         <v>1.04</v>
       </c>
       <c r="N46">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P46">
         <v>0</v>
@@ -6007,7 +6030,7 @@
         <v>116.32</v>
       </c>
       <c r="AD46">
-        <v>17.74</v>
+        <v>17.739999999999998</v>
       </c>
       <c r="AE46">
         <v>167.16</v>
@@ -6036,7 +6059,7 @@
         <v>82</v>
       </c>
       <c r="B47">
-        <v>95.26537997587454</v>
+        <v>95.265379975874538</v>
       </c>
       <c r="C47">
         <v>720</v>
@@ -6048,22 +6071,22 @@
         <v>2.93</v>
       </c>
       <c r="F47">
-        <v>0.2232907154075359</v>
+        <v>0.22329071540753589</v>
       </c>
       <c r="G47">
         <v>5.27</v>
       </c>
       <c r="H47">
-        <v>1.429166440845595</v>
+        <v>1.4291664408455951</v>
       </c>
       <c r="I47">
-        <v>55.21600036621093</v>
+        <v>55.216000366210928</v>
       </c>
       <c r="J47">
-        <v>53.74050025939941</v>
+        <v>53.740500259399411</v>
       </c>
       <c r="K47">
-        <v>49.20500007629394</v>
+        <v>49.205000076293942</v>
       </c>
       <c r="L47">
         <v>35.17925004005432</v>
@@ -6072,7 +6095,7 @@
         <v>1.03</v>
       </c>
       <c r="N47">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P47">
         <v>2</v>
@@ -6087,7 +6110,7 @@
         <v>0</v>
       </c>
       <c r="T47">
-        <v>2.222222222222222</v>
+        <v>2.2222222222222219</v>
       </c>
       <c r="U47" t="b">
         <v>0</v>
@@ -6146,7 +6169,7 @@
         <v>83</v>
       </c>
       <c r="B48">
-        <v>91.70687575392039</v>
+        <v>91.706875753920386</v>
       </c>
       <c r="C48">
         <v>105</v>
@@ -6158,7 +6181,7 @@
         <v>1.86</v>
       </c>
       <c r="F48">
-        <v>-0.6182208907785033</v>
+        <v>-0.61822089077850328</v>
       </c>
       <c r="G48">
         <v>1.67</v>
@@ -6167,16 +6190,16 @@
         <v>-1.087723490014896</v>
       </c>
       <c r="I48">
-        <v>599.4599975585937</v>
+        <v>599.45999755859373</v>
       </c>
       <c r="J48">
-        <v>603.6690002441406</v>
+        <v>603.66900024414065</v>
       </c>
       <c r="K48">
-        <v>586.1760009765625</v>
+        <v>586.17600097656248</v>
       </c>
       <c r="L48">
-        <v>525.4148506164551</v>
+        <v>525.41485061645506</v>
       </c>
       <c r="M48">
         <v>0.99</v>
@@ -6227,10 +6250,10 @@
         <v>37.58</v>
       </c>
       <c r="AD48">
-        <v>36.13</v>
+        <v>36.130000000000003</v>
       </c>
       <c r="AE48">
-        <v>16.76</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="AF48">
         <v>9.26</v>
@@ -6248,7 +6271,7 @@
         <v>159</v>
       </c>
       <c r="AK48">
-        <v>23.55232770066402</v>
+        <v>23.552327700664019</v>
       </c>
     </row>
     <row r="49" spans="1:37">
@@ -6268,31 +6291,31 @@
         <v>1.84</v>
       </c>
       <c r="F49">
-        <v>-0.6339500796791769</v>
+        <v>-0.63395007967917694</v>
       </c>
       <c r="G49">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="H49">
-        <v>-0.5004491728141153</v>
+        <v>-0.50044917281411527</v>
       </c>
       <c r="I49">
         <v>207.1499969482422</v>
       </c>
       <c r="J49">
-        <v>202.690998840332</v>
+        <v>202.69099884033201</v>
       </c>
       <c r="K49">
-        <v>181.9727993774414</v>
+        <v>181.97279937744139</v>
       </c>
       <c r="L49">
-        <v>160.7481497192383</v>
+        <v>160.74814971923831</v>
       </c>
       <c r="M49">
         <v>1.02</v>
       </c>
       <c r="N49">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P49">
         <v>1</v>
@@ -6307,7 +6330,7 @@
         <v>2</v>
       </c>
       <c r="T49">
-        <v>3.888888888888889</v>
+        <v>3.8888888888888888</v>
       </c>
       <c r="U49" t="b">
         <v>1</v>
@@ -6334,7 +6357,7 @@
         <v>14.43</v>
       </c>
       <c r="AC49">
-        <v>39.52</v>
+        <v>39.520000000000003</v>
       </c>
       <c r="AD49">
         <v>43.57</v>
@@ -6346,7 +6369,7 @@
         <v>-7.35</v>
       </c>
       <c r="AG49">
-        <v>-67.73999999999999</v>
+        <v>-67.739999999999995</v>
       </c>
       <c r="AH49" t="s">
         <v>138</v>
@@ -6358,7 +6381,7 @@
         <v>186</v>
       </c>
       <c r="AK49">
-        <v>23.43022979197706</v>
+        <v>23.430229791977059</v>
       </c>
     </row>
     <row r="50" spans="1:37">
@@ -6366,7 +6389,7 @@
         <v>85</v>
       </c>
       <c r="B50">
-        <v>97.88902291917974</v>
+        <v>97.889022919179737</v>
       </c>
       <c r="C50">
         <v>2910</v>
@@ -6375,31 +6398,31 @@
         <v>24.61</v>
       </c>
       <c r="E50">
-        <v>2.32</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="F50">
-        <v>-0.25644954606301</v>
+        <v>-0.25644954606301001</v>
       </c>
       <c r="G50">
         <v>4.38</v>
       </c>
       <c r="H50">
-        <v>0.806935319049529</v>
+        <v>0.80693531904952898</v>
       </c>
       <c r="I50">
-        <v>24.14800033569336</v>
+        <v>24.148000335693361</v>
       </c>
       <c r="J50">
-        <v>25.7329999923706</v>
+        <v>25.732999992370601</v>
       </c>
       <c r="K50">
-        <v>22.26940008163452</v>
+        <v>22.269400081634519</v>
       </c>
       <c r="L50">
         <v>17.17939999103546</v>
       </c>
       <c r="M50">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="N50">
         <v>1.08</v>
@@ -6417,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="T50">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U50" t="b">
         <v>0</v>
@@ -6441,7 +6464,7 @@
         <v>-2.11</v>
       </c>
       <c r="AB50">
-        <v>40.34</v>
+        <v>40.340000000000003</v>
       </c>
       <c r="AC50">
         <v>32.54</v>
@@ -6476,7 +6499,7 @@
         <v>86</v>
       </c>
       <c r="B51">
-        <v>94.84318455971049</v>
+        <v>94.843184559710494</v>
       </c>
       <c r="C51">
         <v>180</v>
@@ -6488,16 +6511,16 @@
         <v>2.6</v>
       </c>
       <c r="F51">
-        <v>-0.03624090145357904</v>
+        <v>-3.6240901453579041E-2</v>
       </c>
       <c r="G51">
-        <v>2.47</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="H51">
         <v>-0.5284146164903426</v>
       </c>
       <c r="I51">
-        <v>199.0860015869141</v>
+        <v>199.08600158691411</v>
       </c>
       <c r="J51">
         <v>195.5940017700195</v>
@@ -6506,7 +6529,7 @@
         <v>194.6864001464844</v>
       </c>
       <c r="L51">
-        <v>168.9075499725342</v>
+        <v>168.90754997253421</v>
       </c>
       <c r="M51">
         <v>1.02</v>
@@ -6545,7 +6568,7 @@
         <v>212.6</v>
       </c>
       <c r="Z51">
-        <v>1070.14</v>
+        <v>1070.1400000000001</v>
       </c>
       <c r="AA51">
         <v>18.23</v>
@@ -6578,7 +6601,7 @@
         <v>188</v>
       </c>
       <c r="AK51">
-        <v>23.2362121315264</v>
+        <v>23.236212131526401</v>
       </c>
     </row>
     <row r="52" spans="1:37">
@@ -6586,7 +6609,7 @@
         <v>87</v>
       </c>
       <c r="B52">
-        <v>98.64294330518698</v>
+        <v>98.642943305186975</v>
       </c>
       <c r="C52">
         <v>1549</v>
@@ -6598,31 +6621,31 @@
         <v>3.72</v>
       </c>
       <c r="F52">
-        <v>0.8445936769841442</v>
+        <v>0.84459367698414423</v>
       </c>
       <c r="G52">
         <v>2.98</v>
       </c>
       <c r="H52">
-        <v>-0.1718552096184399</v>
+        <v>-0.17185520961843989</v>
       </c>
       <c r="I52">
-        <v>64.01000061035157</v>
+        <v>64.010000610351568</v>
       </c>
       <c r="J52">
-        <v>60.25550003051758</v>
+        <v>60.255500030517581</v>
       </c>
       <c r="K52">
-        <v>56.03399993896485</v>
+        <v>56.033999938964847</v>
       </c>
       <c r="L52">
-        <v>39.00465006828308</v>
+        <v>39.004650068283077</v>
       </c>
       <c r="M52">
         <v>1.06</v>
       </c>
       <c r="N52">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -6688,7 +6711,7 @@
         <v>171</v>
       </c>
       <c r="AK52">
-        <v>23.05464317295253</v>
+        <v>23.054643172952531</v>
       </c>
     </row>
     <row r="53" spans="1:37">
@@ -6696,7 +6719,7 @@
         <v>88</v>
       </c>
       <c r="B53">
-        <v>92.8226779252111</v>
+        <v>92.822677925211096</v>
       </c>
       <c r="C53">
         <v>3695</v>
@@ -6708,25 +6731,25 @@
         <v>2.06</v>
       </c>
       <c r="F53">
-        <v>-0.460929001771767</v>
+        <v>-0.46092900177176699</v>
       </c>
       <c r="G53">
         <v>2.42</v>
       </c>
       <c r="H53">
-        <v>-0.5633714210856274</v>
+        <v>-0.56337142108562743</v>
       </c>
       <c r="I53">
-        <v>105.4399993896484</v>
+        <v>105.43999938964841</v>
       </c>
       <c r="J53">
         <v>108.0864994049072</v>
       </c>
       <c r="K53">
-        <v>102.018999786377</v>
+        <v>102.01899978637699</v>
       </c>
       <c r="L53">
-        <v>90.66479984283447</v>
+        <v>90.664799842834469</v>
       </c>
       <c r="M53">
         <v>0.98</v>
@@ -6798,7 +6821,7 @@
         <v>189</v>
       </c>
       <c r="AK53">
-        <v>22.95347034015968</v>
+        <v>22.953470340159679</v>
       </c>
     </row>
     <row r="54" spans="1:37">
@@ -6815,28 +6838,28 @@
         <v>209.3</v>
       </c>
       <c r="E54">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F54">
-        <v>-1.176607096752417</v>
+        <v>-1.1766070967524169</v>
       </c>
       <c r="G54">
         <v>3.27</v>
       </c>
       <c r="H54">
-        <v>0.03089425703421086</v>
+        <v>3.0894257034210861E-2</v>
       </c>
       <c r="I54">
-        <v>208.1660003662109</v>
+        <v>208.16600036621091</v>
       </c>
       <c r="J54">
-        <v>213.7520011901856</v>
+        <v>213.75200119018561</v>
       </c>
       <c r="K54">
-        <v>199.9624002075195</v>
+        <v>199.96240020751949</v>
       </c>
       <c r="L54">
-        <v>172.7386997222901</v>
+        <v>172.73869972229011</v>
       </c>
       <c r="M54">
         <v>0.97</v>
@@ -6875,7 +6898,7 @@
         <v>222.97</v>
       </c>
       <c r="Z54">
-        <v>40.52</v>
+        <v>40.520000000000003</v>
       </c>
       <c r="AA54">
         <v>12.9</v>
@@ -6890,10 +6913,10 @@
         <v>21.91</v>
       </c>
       <c r="AE54">
-        <v>32.48</v>
+        <v>32.479999999999997</v>
       </c>
       <c r="AF54">
-        <v>9.029999999999999</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="AG54">
         <v>-49.12</v>
@@ -6916,7 +6939,7 @@
         <v>90</v>
       </c>
       <c r="B55">
-        <v>91.22436670687576</v>
+        <v>91.224366706875756</v>
       </c>
       <c r="C55">
         <v>2567</v>
@@ -6928,31 +6951,31 @@
         <v>1.63</v>
       </c>
       <c r="F55">
-        <v>-0.7991065631362502</v>
+        <v>-0.79910656313625017</v>
       </c>
       <c r="G55">
         <v>1.94</v>
       </c>
       <c r="H55">
-        <v>-0.8989567452003596</v>
+        <v>-0.89895674520035962</v>
       </c>
       <c r="I55">
-        <v>48.2739990234375</v>
+        <v>48.273999023437497</v>
       </c>
       <c r="J55">
-        <v>47.17299995422363</v>
+        <v>47.172999954223627</v>
       </c>
       <c r="K55">
-        <v>43.65979995727539</v>
+        <v>43.659799957275389</v>
       </c>
       <c r="L55">
-        <v>39.86430004119873</v>
+        <v>39.864300041198732</v>
       </c>
       <c r="M55">
         <v>1.02</v>
       </c>
       <c r="N55">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -6988,7 +7011,7 @@
         <v>1.93</v>
       </c>
       <c r="AA55">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AB55">
         <v>11.35</v>
@@ -7018,7 +7041,7 @@
         <v>191</v>
       </c>
       <c r="AK55">
-        <v>21.70671544019008</v>
+        <v>21.706715440190081</v>
       </c>
     </row>
     <row r="56" spans="1:37">
@@ -7026,7 +7049,7 @@
         <v>91</v>
       </c>
       <c r="B56">
-        <v>93.66706875753921</v>
+        <v>93.667068757539212</v>
       </c>
       <c r="C56">
         <v>901</v>
@@ -7041,22 +7064,22 @@
         <v>-0.5238457573744616</v>
       </c>
       <c r="G56">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="H56">
-        <v>-0.8080690532526197</v>
+        <v>-0.80806905325261968</v>
       </c>
       <c r="I56">
-        <v>235.7319976806641</v>
+        <v>235.73199768066411</v>
       </c>
       <c r="J56">
-        <v>243.5574989318848</v>
+        <v>243.55749893188479</v>
       </c>
       <c r="K56">
         <v>227.038600769043</v>
       </c>
       <c r="L56">
-        <v>171.4620499801636</v>
+        <v>171.46204998016361</v>
       </c>
       <c r="M56">
         <v>0.97</v>
@@ -7113,7 +7136,7 @@
         <v>27.11</v>
       </c>
       <c r="AF56">
-        <v>137.14</v>
+        <v>137.13999999999999</v>
       </c>
       <c r="AG56">
         <v>28.44</v>
@@ -7128,7 +7151,7 @@
         <v>182</v>
       </c>
       <c r="AK56">
-        <v>21.45763273017051</v>
+        <v>21.457632730170509</v>
       </c>
     </row>
     <row r="57" spans="1:37">
@@ -7136,37 +7159,37 @@
         <v>92</v>
       </c>
       <c r="B57">
-        <v>94.16465621230398</v>
+        <v>94.164656212303981</v>
       </c>
       <c r="C57">
         <v>2741</v>
       </c>
       <c r="D57">
-        <v>65.59999999999999</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="E57">
         <v>2.33</v>
       </c>
       <c r="F57">
-        <v>-0.248584951612673</v>
+        <v>-0.24858495161267299</v>
       </c>
       <c r="G57">
         <v>2.46</v>
       </c>
       <c r="H57">
-        <v>-0.5354059774093998</v>
+        <v>-0.53540597740939977</v>
       </c>
       <c r="I57">
-        <v>63.68999938964843</v>
+        <v>63.689999389648428</v>
       </c>
       <c r="J57">
-        <v>66.78899993896485</v>
+        <v>66.788999938964849</v>
       </c>
       <c r="K57">
-        <v>64.20259994506836</v>
+        <v>64.202599945068357</v>
       </c>
       <c r="L57">
-        <v>53.41104988098144</v>
+        <v>53.411049880981437</v>
       </c>
       <c r="M57">
         <v>0.95</v>
@@ -7199,7 +7222,7 @@
         <v>0</v>
       </c>
       <c r="X57">
-        <v>32.55</v>
+        <v>32.549999999999997</v>
       </c>
       <c r="Y57">
         <v>73.42</v>
@@ -7211,7 +7234,7 @@
         <v>28.17</v>
       </c>
       <c r="AB57">
-        <v>17.31</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="AC57">
         <v>61.5</v>
@@ -7246,7 +7269,7 @@
         <v>93</v>
       </c>
       <c r="B58">
-        <v>93.33534378769602</v>
+        <v>93.335343787696019</v>
       </c>
       <c r="C58">
         <v>4255</v>
@@ -7255,7 +7278,7 @@
         <v>82</v>
       </c>
       <c r="E58">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="F58">
         <v>-0.1227514404072839</v>
@@ -7264,25 +7287,25 @@
         <v>2.65</v>
       </c>
       <c r="H58">
-        <v>-0.4025701199473183</v>
+        <v>-0.40257011994731828</v>
       </c>
       <c r="I58">
-        <v>81.09199981689453</v>
+        <v>81.091999816894528</v>
       </c>
       <c r="J58">
-        <v>78.6452507019043</v>
+        <v>78.645250701904303</v>
       </c>
       <c r="K58">
-        <v>71.26270065307617</v>
+        <v>71.262700653076166</v>
       </c>
       <c r="L58">
-        <v>52.12510017395019</v>
+        <v>52.125100173950187</v>
       </c>
       <c r="M58">
         <v>1.03</v>
       </c>
       <c r="N58">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P58">
         <v>2</v>
@@ -7348,7 +7371,7 @@
         <v>171</v>
       </c>
       <c r="AK58">
-        <v>20.93331912066379</v>
+        <v>20.933319120663789</v>
       </c>
     </row>
     <row r="59" spans="1:37">
@@ -7356,7 +7379,7 @@
         <v>94</v>
       </c>
       <c r="B59">
-        <v>91.79734620024126</v>
+        <v>91.797346200241265</v>
       </c>
       <c r="C59">
         <v>132</v>
@@ -7368,25 +7391,25 @@
         <v>1.55</v>
       </c>
       <c r="F59">
-        <v>-0.8620233187389446</v>
+        <v>-0.86202331873894456</v>
       </c>
       <c r="G59">
         <v>1.95</v>
       </c>
       <c r="H59">
-        <v>-0.8919653842813027</v>
+        <v>-0.89196538428130268</v>
       </c>
       <c r="I59">
-        <v>13.09999980926514</v>
+        <v>13.099999809265141</v>
       </c>
       <c r="J59">
-        <v>13.36449995040894</v>
+        <v>13.364499950408939</v>
       </c>
       <c r="K59">
         <v>13.08079999923706</v>
       </c>
       <c r="L59">
-        <v>11.4783499956131</v>
+        <v>11.478349995613099</v>
       </c>
       <c r="M59">
         <v>0.98</v>
@@ -7434,7 +7457,7 @@
         <v>30.41</v>
       </c>
       <c r="AC59">
-        <v>32.63</v>
+        <v>32.630000000000003</v>
       </c>
       <c r="AD59">
         <v>7.31</v>
@@ -7466,7 +7489,7 @@
         <v>95</v>
       </c>
       <c r="B60">
-        <v>94.20989143546441</v>
+        <v>94.209891435464414</v>
       </c>
       <c r="C60">
         <v>357</v>
@@ -7484,25 +7507,25 @@
         <v>2.36</v>
       </c>
       <c r="H60">
-        <v>-0.605319586599969</v>
+        <v>-0.60531958659996898</v>
       </c>
       <c r="I60">
         <v>111.197998046875</v>
       </c>
       <c r="J60">
-        <v>107.0194995880127</v>
+        <v>107.01949958801271</v>
       </c>
       <c r="K60">
         <v>102.4202502441406</v>
       </c>
       <c r="L60">
-        <v>86.45716262817383</v>
+        <v>86.457162628173833</v>
       </c>
       <c r="M60">
         <v>1.04</v>
       </c>
       <c r="N60">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P60">
         <v>0</v>
@@ -7544,7 +7567,7 @@
         <v>26.28</v>
       </c>
       <c r="AC60">
-        <v>35.95</v>
+        <v>35.950000000000003</v>
       </c>
       <c r="AD60">
         <v>33.83</v>
@@ -7582,13 +7605,13 @@
         <v>479</v>
       </c>
       <c r="D61">
-        <v>65.45999999999999</v>
+        <v>65.459999999999994</v>
       </c>
       <c r="E61">
         <v>1.66</v>
       </c>
       <c r="F61">
-        <v>-0.7755127797852397</v>
+        <v>-0.77551277978523969</v>
       </c>
       <c r="G61">
         <v>3.01</v>
@@ -7597,16 +7620,16 @@
         <v>-0.1508811268612692</v>
       </c>
       <c r="I61">
-        <v>65.19199905395507</v>
+        <v>65.191999053955072</v>
       </c>
       <c r="J61">
-        <v>66.96799945831299</v>
+        <v>66.967999458312988</v>
       </c>
       <c r="K61">
-        <v>62.57759994506836</v>
+        <v>62.577599945068357</v>
       </c>
       <c r="L61">
-        <v>50.06915006637573</v>
+        <v>50.069150066375727</v>
       </c>
       <c r="M61">
         <v>0.97</v>
@@ -7678,7 +7701,7 @@
         <v>169</v>
       </c>
       <c r="AK61">
-        <v>20.13133503662099</v>
+        <v>20.131335036620989</v>
       </c>
     </row>
     <row r="62" spans="1:37">
@@ -7686,7 +7709,7 @@
         <v>97</v>
       </c>
       <c r="B62">
-        <v>96.20024125452352</v>
+        <v>96.200241254523519</v>
       </c>
       <c r="C62">
         <v>3641</v>
@@ -7698,25 +7721,25 @@
         <v>1.82</v>
       </c>
       <c r="F62">
-        <v>-0.6496792685798506</v>
+        <v>-0.64967926857985059</v>
       </c>
       <c r="G62">
         <v>2.14</v>
       </c>
       <c r="H62">
-        <v>-0.7591295268192211</v>
+        <v>-0.75912952681922108</v>
       </c>
       <c r="I62">
         <v>59.15</v>
       </c>
       <c r="J62">
-        <v>61.46600036621093</v>
+        <v>61.466000366210928</v>
       </c>
       <c r="K62">
-        <v>54.85780029296875</v>
+        <v>54.857800292968747</v>
       </c>
       <c r="L62">
-        <v>39.53305012702942</v>
+        <v>39.533050127029419</v>
       </c>
       <c r="M62">
         <v>0.96</v>
@@ -7737,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="T62">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U62" t="b">
         <v>0</v>
@@ -7752,7 +7775,7 @@
         <v>21.98</v>
       </c>
       <c r="Y62">
-        <v>66.18000000000001</v>
+        <v>66.180000000000007</v>
       </c>
       <c r="Z62">
         <v>1.05</v>
@@ -7776,7 +7799,7 @@
         <v>8.82</v>
       </c>
       <c r="AG62">
-        <v>17.24</v>
+        <v>17.239999999999998</v>
       </c>
       <c r="AH62" t="s">
         <v>118</v>
@@ -7796,7 +7819,7 @@
         <v>98</v>
       </c>
       <c r="B63">
-        <v>93.45597104945718</v>
+        <v>93.455971049457176</v>
       </c>
       <c r="C63">
         <v>5399</v>
@@ -7805,7 +7828,7 @@
         <v>46.31</v>
       </c>
       <c r="E63">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="F63">
         <v>1.741157444322541</v>
@@ -7814,25 +7837,25 @@
         <v>4.58</v>
       </c>
       <c r="H63">
-        <v>0.9467625374306675</v>
+        <v>0.94676253743066752</v>
       </c>
       <c r="I63">
-        <v>45.93800048828125</v>
+        <v>45.938000488281247</v>
       </c>
       <c r="J63">
-        <v>45.50500030517578</v>
+        <v>45.505000305175777</v>
       </c>
       <c r="K63">
-        <v>42.28799995422364</v>
+        <v>42.287999954223643</v>
       </c>
       <c r="L63">
-        <v>34.76628499984741</v>
+        <v>34.766284999847407</v>
       </c>
       <c r="M63">
         <v>1.01</v>
       </c>
       <c r="N63">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P63">
         <v>0</v>
@@ -7906,7 +7929,7 @@
         <v>99</v>
       </c>
       <c r="B64">
-        <v>91.28468033775633</v>
+        <v>91.284680337756328</v>
       </c>
       <c r="C64">
         <v>1209</v>
@@ -7918,25 +7941,25 @@
         <v>2.59</v>
       </c>
       <c r="F64">
-        <v>-0.04410549590391603</v>
+        <v>-4.4105495903916027E-2</v>
       </c>
       <c r="G64">
         <v>6.27</v>
       </c>
       <c r="H64">
-        <v>2.128302532751287</v>
+        <v>2.1283025327512868</v>
       </c>
       <c r="I64">
-        <v>6.667999935150147</v>
+        <v>6.6679999351501467</v>
       </c>
       <c r="J64">
-        <v>6.820000004768372</v>
+        <v>6.8200000047683718</v>
       </c>
       <c r="K64">
-        <v>6.155400009155273</v>
+        <v>6.1554000091552732</v>
       </c>
       <c r="L64">
-        <v>4.757875000238418</v>
+        <v>4.7578750002384176</v>
       </c>
       <c r="M64">
         <v>0.98</v>
@@ -7957,7 +7980,7 @@
         <v>0</v>
       </c>
       <c r="T64">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U64" t="b">
         <v>0</v>
@@ -7975,16 +7998,16 @@
         <v>7.9</v>
       </c>
       <c r="Z64">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AA64" t="s">
         <v>111</v>
       </c>
       <c r="AB64">
-        <v>40.38</v>
+        <v>40.380000000000003</v>
       </c>
       <c r="AC64">
-        <v>8.199999999999999</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AD64">
         <v>8.56</v>
@@ -7996,7 +8019,7 @@
         <v>50</v>
       </c>
       <c r="AG64">
-        <v>-9.710000000000001</v>
+        <v>-9.7100000000000009</v>
       </c>
       <c r="AH64" t="s">
         <v>122</v>
@@ -8008,7 +8031,7 @@
         <v>158</v>
       </c>
       <c r="AK64">
-        <v>18.22669952600353</v>
+        <v>18.226699526003529</v>
       </c>
     </row>
     <row r="65" spans="1:37">
@@ -8016,7 +8039,7 @@
         <v>100</v>
       </c>
       <c r="B65">
-        <v>96.60735826296744</v>
+        <v>96.607358262967438</v>
       </c>
       <c r="C65">
         <v>1050</v>
@@ -8028,31 +8051,31 @@
         <v>2.62</v>
       </c>
       <c r="F65">
-        <v>-0.0205117125529054</v>
+        <v>-2.05117125529054E-2</v>
       </c>
       <c r="G65">
-        <v>4.15</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="H65">
-        <v>0.6461340179112202</v>
+        <v>0.64613401791122016</v>
       </c>
       <c r="I65">
-        <v>623.4460083007813</v>
+        <v>623.44600830078127</v>
       </c>
       <c r="J65">
-        <v>643.7270050048828</v>
+        <v>643.72700500488281</v>
       </c>
       <c r="K65">
         <v>559.2580010986328</v>
       </c>
       <c r="L65">
-        <v>384.9229507446289</v>
+        <v>384.92295074462891</v>
       </c>
       <c r="M65">
         <v>0.97</v>
       </c>
       <c r="N65">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P65">
         <v>0</v>
@@ -8067,7 +8090,7 @@
         <v>0</v>
       </c>
       <c r="T65">
-        <v>2.222222222222222</v>
+        <v>2.2222222222222219</v>
       </c>
       <c r="U65" t="b">
         <v>0</v>
@@ -8103,7 +8126,7 @@
         <v>64.81</v>
       </c>
       <c r="AF65">
-        <v>-69.48999999999999</v>
+        <v>-69.489999999999995</v>
       </c>
       <c r="AG65">
         <v>139.19</v>
@@ -8126,7 +8149,7 @@
         <v>101</v>
       </c>
       <c r="B66">
-        <v>96.68275030156815</v>
+        <v>96.682750301568149</v>
       </c>
       <c r="C66">
         <v>2293</v>
@@ -8138,25 +8161,25 @@
         <v>2.15</v>
       </c>
       <c r="F66">
-        <v>-0.3901476517187358</v>
+        <v>-0.39014765171873578</v>
       </c>
       <c r="G66">
         <v>2.66</v>
       </c>
       <c r="H66">
-        <v>-0.3955787590282612</v>
+        <v>-0.39557875902826117</v>
       </c>
       <c r="I66">
-        <v>79.94199981689454</v>
+        <v>79.941999816894537</v>
       </c>
       <c r="J66">
-        <v>81.4745002746582</v>
+        <v>81.474500274658197</v>
       </c>
       <c r="K66">
-        <v>74.92939994812012</v>
+        <v>74.929399948120121</v>
       </c>
       <c r="L66">
-        <v>56.93799993515015</v>
+        <v>56.937999935150152</v>
       </c>
       <c r="M66">
         <v>0.98</v>
@@ -8213,7 +8236,7 @@
         <v>18.48</v>
       </c>
       <c r="AF66">
-        <v>162.86</v>
+        <v>162.86000000000001</v>
       </c>
       <c r="AG66">
         <v>-51.39</v>
@@ -8228,7 +8251,7 @@
         <v>170</v>
       </c>
       <c r="AK66">
-        <v>17.89166447850017</v>
+        <v>17.891664478500171</v>
       </c>
     </row>
     <row r="67" spans="1:37">
@@ -8248,25 +8271,25 @@
         <v>1.68</v>
       </c>
       <c r="F67">
-        <v>-0.759783590884566</v>
+        <v>-0.75978359088456604</v>
       </c>
       <c r="G67">
         <v>2.46</v>
       </c>
       <c r="H67">
-        <v>-0.5354059774093998</v>
+        <v>-0.53540597740939977</v>
       </c>
       <c r="I67">
-        <v>24.7439998626709</v>
+        <v>24.743999862670901</v>
       </c>
       <c r="J67">
-        <v>25.59349994659424</v>
+        <v>25.593499946594239</v>
       </c>
       <c r="K67">
-        <v>23.97539989471436</v>
+        <v>23.975399894714361</v>
       </c>
       <c r="L67">
-        <v>19.53899998188019</v>
+        <v>19.538999981880188</v>
       </c>
       <c r="M67">
         <v>0.97</v>
@@ -8311,10 +8334,10 @@
         <v>4.87</v>
       </c>
       <c r="AB67">
-        <v>17.42</v>
+        <v>17.420000000000002</v>
       </c>
       <c r="AC67">
-        <v>18.99</v>
+        <v>18.989999999999998</v>
       </c>
       <c r="AD67">
         <v>8.08</v>
@@ -8323,7 +8346,7 @@
         <v>271.43</v>
       </c>
       <c r="AF67">
-        <v>16.67</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="AG67">
         <v>20</v>
@@ -8338,7 +8361,7 @@
         <v>166</v>
       </c>
       <c r="AK67">
-        <v>16.61119272636262</v>
+        <v>16.611192726362621</v>
       </c>
     </row>
     <row r="68" spans="1:37">
@@ -8346,7 +8369,7 @@
         <v>103</v>
       </c>
       <c r="B68">
-        <v>95.12967430639324</v>
+        <v>95.129674306393241</v>
       </c>
       <c r="C68">
         <v>21</v>
@@ -8358,25 +8381,25 @@
         <v>6.72</v>
       </c>
       <c r="F68">
-        <v>3.203972012085188</v>
+        <v>3.2039720120851878</v>
       </c>
       <c r="G68">
         <v>4.28</v>
       </c>
       <c r="H68">
-        <v>0.73702170985896</v>
+        <v>0.73702170985895998</v>
       </c>
       <c r="I68">
-        <v>227.0619995117187</v>
+        <v>227.06199951171871</v>
       </c>
       <c r="J68">
         <v>191.5625</v>
       </c>
       <c r="K68">
-        <v>180.9484005737305</v>
+        <v>180.94840057373051</v>
       </c>
       <c r="L68">
-        <v>157.7213702774048</v>
+        <v>157.72137027740479</v>
       </c>
       <c r="M68">
         <v>1.19</v>
@@ -8436,7 +8459,7 @@
         <v>55.63</v>
       </c>
       <c r="AG68">
-        <v>-65.56999999999999</v>
+        <v>-65.569999999999993</v>
       </c>
       <c r="AH68" t="s">
         <v>126</v>
@@ -8456,7 +8479,7 @@
         <v>104</v>
       </c>
       <c r="B69">
-        <v>93.13932448733414</v>
+        <v>93.139324487334136</v>
       </c>
       <c r="C69">
         <v>1246</v>
@@ -8474,7 +8497,7 @@
         <v>1.57</v>
       </c>
       <c r="H69">
-        <v>-1.157637099205466</v>
+        <v>-1.1576370992054661</v>
       </c>
       <c r="I69">
         <v>10.10200004577637</v>
@@ -8483,10 +8506,10 @@
         <v>10.30250005722046</v>
       </c>
       <c r="K69">
-        <v>9.995800056457519</v>
+        <v>9.9958000564575187</v>
       </c>
       <c r="L69">
-        <v>8.660650024414062</v>
+        <v>8.6606500244140623</v>
       </c>
       <c r="M69">
         <v>0.98</v>
@@ -8531,7 +8554,7 @@
         <v>25.17</v>
       </c>
       <c r="AB69">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AC69">
         <v>47.31</v>
@@ -8560,34 +8583,34 @@
         <v>105</v>
       </c>
       <c r="B70">
-        <v>92.09891435464415</v>
+        <v>92.098914354644151</v>
       </c>
       <c r="C70">
         <v>1723</v>
       </c>
       <c r="D70">
-        <v>35.41</v>
+        <v>35.409999999999997</v>
       </c>
       <c r="E70">
         <v>1.69</v>
       </c>
       <c r="F70">
-        <v>-0.7519189964342292</v>
+        <v>-0.75191899643422921</v>
       </c>
       <c r="G70">
         <v>1.8</v>
       </c>
       <c r="H70">
-        <v>-0.9968357980671564</v>
+        <v>-0.99683579806715639</v>
       </c>
       <c r="I70">
-        <v>35.28200073242188</v>
+        <v>35.282000732421878</v>
       </c>
       <c r="J70">
-        <v>36.46675033569336</v>
+        <v>36.466750335693362</v>
       </c>
       <c r="K70">
-        <v>34.68859996795654</v>
+        <v>34.688599967956542</v>
       </c>
       <c r="L70">
         <v>27.6196500492096</v>
@@ -8626,7 +8649,7 @@
         <v>16.02</v>
       </c>
       <c r="Y70">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="Z70">
         <v>5.63</v>
@@ -8635,7 +8658,7 @@
         <v>-12.55</v>
       </c>
       <c r="AB70">
-        <v>73.06999999999999</v>
+        <v>73.069999999999993</v>
       </c>
       <c r="AC70">
         <v>2.37</v>
@@ -8644,7 +8667,7 @@
         <v>14.12</v>
       </c>
       <c r="AE70">
-        <v>-8.449999999999999</v>
+        <v>-8.4499999999999993</v>
       </c>
       <c r="AF70">
         <v>20.34</v>
@@ -8670,7 +8693,7 @@
         <v>106</v>
       </c>
       <c r="B71">
-        <v>91.14897466827503</v>
+        <v>91.148974668275031</v>
       </c>
       <c r="C71">
         <v>1634</v>
@@ -8682,28 +8705,28 @@
         <v>3.59</v>
       </c>
       <c r="F71">
-        <v>0.7423539491297654</v>
+        <v>0.74235394912976538</v>
       </c>
       <c r="G71">
         <v>2.63</v>
       </c>
       <c r="H71">
-        <v>-0.4165528417854321</v>
+        <v>-0.41655284178543212</v>
       </c>
       <c r="I71">
-        <v>116.5080001831055</v>
+        <v>116.50800018310549</v>
       </c>
       <c r="J71">
         <v>107.2147495269775</v>
       </c>
       <c r="K71">
-        <v>98.69909973144532</v>
+        <v>98.699099731445315</v>
       </c>
       <c r="L71">
-        <v>90.23699989318848</v>
+        <v>90.236999893188482</v>
       </c>
       <c r="M71">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N71">
         <v>1.18</v>
@@ -8780,7 +8803,7 @@
         <v>107</v>
       </c>
       <c r="B72">
-        <v>90.41013268998793</v>
+        <v>90.410132689987933</v>
       </c>
       <c r="C72">
         <v>680</v>
@@ -8792,7 +8815,7 @@
         <v>1.49</v>
       </c>
       <c r="F72">
-        <v>-0.9092108854409655</v>
+        <v>-0.90921088544096551</v>
       </c>
       <c r="G72">
         <v>1.69</v>
@@ -8801,16 +8824,16 @@
         <v>-1.073740768176783</v>
       </c>
       <c r="I72">
-        <v>295.9299926757812</v>
+        <v>295.92999267578119</v>
       </c>
       <c r="J72">
-        <v>300.901496887207</v>
+        <v>300.90149688720697</v>
       </c>
       <c r="K72">
-        <v>288.7931982421875</v>
+        <v>288.79319824218749</v>
       </c>
       <c r="L72">
-        <v>252.7366496276856</v>
+        <v>252.73664962768561</v>
       </c>
       <c r="M72">
         <v>0.98</v>
@@ -8882,7 +8905,7 @@
         <v>169</v>
       </c>
       <c r="AK72">
-        <v>13.6477161795567</v>
+        <v>13.647716179556699</v>
       </c>
     </row>
     <row r="73" spans="1:37">
@@ -8890,7 +8913,7 @@
         <v>108</v>
       </c>
       <c r="B73">
-        <v>93.21471652593486</v>
+        <v>93.214716525934861</v>
       </c>
       <c r="C73">
         <v>731</v>
@@ -8902,22 +8925,22 @@
         <v>2.61</v>
       </c>
       <c r="F73">
-        <v>-0.02837630700324239</v>
+        <v>-2.8376307003242389E-2</v>
       </c>
       <c r="G73">
         <v>4.18</v>
       </c>
       <c r="H73">
-        <v>0.6671081006683904</v>
+        <v>0.66710810066839044</v>
       </c>
       <c r="I73">
-        <v>186.8140014648438</v>
+        <v>186.81400146484381</v>
       </c>
       <c r="J73">
         <v>184.7980026245117</v>
       </c>
       <c r="K73">
-        <v>157.7080004882812</v>
+        <v>157.70800048828119</v>
       </c>
       <c r="L73">
         <v>149.1681749343872</v>
@@ -8953,7 +8976,7 @@
         <v>0</v>
       </c>
       <c r="X73">
-        <v>95.76000000000001</v>
+        <v>95.76</v>
       </c>
       <c r="Y73">
         <v>199.42</v>
@@ -8992,7 +9015,7 @@
         <v>197</v>
       </c>
       <c r="AK73">
-        <v>11.92896106539862</v>
+        <v>11.928961065398619</v>
       </c>
     </row>
     <row r="74" spans="1:37">
@@ -9000,7 +9023,7 @@
         <v>109</v>
       </c>
       <c r="B74">
-        <v>93.65199034981906</v>
+        <v>93.651990349819059</v>
       </c>
       <c r="C74">
         <v>84</v>
@@ -9012,22 +9035,22 @@
         <v>1.95</v>
       </c>
       <c r="F74">
-        <v>-0.5474395407254721</v>
+        <v>-0.54743954072547207</v>
       </c>
       <c r="G74">
         <v>2.29</v>
       </c>
       <c r="H74">
-        <v>-0.6542591130333674</v>
+        <v>-0.65425911303336737</v>
       </c>
       <c r="I74">
-        <v>171.2100036621094</v>
+        <v>171.21000366210939</v>
       </c>
       <c r="J74">
         <v>174.2850006103516</v>
       </c>
       <c r="K74">
-        <v>161.3853997802734</v>
+        <v>161.38539978027339</v>
       </c>
       <c r="L74">
         <v>126.9348499679565</v>
@@ -9063,13 +9086,13 @@
         <v>0</v>
       </c>
       <c r="X74">
-        <v>89.76000000000001</v>
+        <v>89.76</v>
       </c>
       <c r="Y74">
         <v>189.49</v>
       </c>
       <c r="Z74">
-        <v>98.93000000000001</v>
+        <v>98.93</v>
       </c>
       <c r="AA74" t="s">
         <v>111</v>
@@ -9122,25 +9145,25 @@
         <v>1.43</v>
       </c>
       <c r="F75">
-        <v>-0.9563984521429864</v>
+        <v>-0.95639845214298636</v>
       </c>
       <c r="G75">
         <v>2.06</v>
       </c>
       <c r="H75">
-        <v>-0.8150604141716765</v>
+        <v>-0.81506041417167652</v>
       </c>
       <c r="I75">
-        <v>38.06000061035157</v>
+        <v>38.060000610351572</v>
       </c>
       <c r="J75">
-        <v>38.65399990081787</v>
+        <v>38.653999900817873</v>
       </c>
       <c r="K75">
-        <v>37.44459999084473</v>
+        <v>37.444599990844729</v>
       </c>
       <c r="L75">
-        <v>32.11335003852844</v>
+        <v>32.113350038528438</v>
       </c>
       <c r="M75">
         <v>0.98</v>
@@ -9191,7 +9214,7 @@
         <v>5.13</v>
       </c>
       <c r="AD75">
-        <v>17.33</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="AE75">
         <v>54.29</v>
@@ -9216,6 +9239,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>